--- a/dati_sremo/sanremo_dati_serate.xlsx
+++ b/dati_sremo/sanremo_dati_serate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/umbertobertonelli/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AAF5F702-EC6E-8142-BAC1-44DE083AF877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E9978F-B887-444E-B5EC-561651833527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39820" yWindow="6160" windowWidth="28040" windowHeight="17180" xr2:uid="{B4699A91-0234-EF40-A7DC-9F915DE8C013}"/>
+    <workbookView xWindow="39800" yWindow="6160" windowWidth="28040" windowHeight="17180" xr2:uid="{B4699A91-0234-EF40-A7DC-9F915DE8C013}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="176">
   <si>
     <t>year</t>
   </si>
@@ -476,12 +476,6 @@
     <t>Marcella Bella</t>
   </si>
   <si>
-    <t>Shablo con Guè</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Joshua e Tormento</t>
-  </si>
-  <si>
     <t>Tony Effe</t>
   </si>
   <si>
@@ -524,7 +518,52 @@
     <t>Elodie e Achille Lauro</t>
   </si>
   <si>
-    <t>Shablo feat. Gue</t>
+    <t>Ron</t>
+  </si>
+  <si>
+    <t>Ornella Vanoni con Bungaro e Pacifico</t>
+  </si>
+  <si>
+    <t>Ermal Meta e Fabrizio Moro</t>
+  </si>
+  <si>
+    <t>Mario Biondi</t>
+  </si>
+  <si>
+    <t>Roby Facchinetti e Riccardo Fogli</t>
+  </si>
+  <si>
+    <t>Decibel</t>
+  </si>
+  <si>
+    <t>Elio e le Storie Tese</t>
+  </si>
+  <si>
+    <t>Giovanni Caccamo</t>
+  </si>
+  <si>
+    <t>Red Canzian</t>
+  </si>
+  <si>
+    <t>Luca Barbarossa</t>
+  </si>
+  <si>
+    <t>Diodato e Roy Paci</t>
+  </si>
+  <si>
+    <t>Nina Zilli</t>
+  </si>
+  <si>
+    <t>Renzo Rubino</t>
+  </si>
+  <si>
+    <t>Enzo Avitabile con Peppe Servillo</t>
+  </si>
+  <si>
+    <t>Shablo feat. Gue  Joshua e Tormento</t>
+  </si>
+  <si>
+    <t>Shablo con Guè  Joshua e Tormento</t>
   </si>
 </sst>
 </file>
@@ -896,8 +935,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{668820A4-AEE7-984A-A205-7DC3CEADC66C}">
-  <dimension ref="A1:I741"/>
+  <dimension ref="A1:H821"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="38.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -16804,7 +16846,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A641">
         <v>2025</v>
       </c>
@@ -16827,7 +16869,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A642">
         <v>2025</v>
       </c>
@@ -16850,7 +16892,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A643">
         <v>2025</v>
       </c>
@@ -16861,22 +16903,19 @@
         <v>8</v>
       </c>
       <c r="D643" t="s">
-        <v>146</v>
-      </c>
-      <c r="E643" t="s">
-        <v>147</v>
+        <v>175</v>
+      </c>
+      <c r="E643">
+        <v>15</v>
       </c>
       <c r="F643">
-        <v>15</v>
-      </c>
-      <c r="G643">
         <v>29</v>
       </c>
-      <c r="I643">
+      <c r="H643">
         <v>18</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A644">
         <v>2025</v>
       </c>
@@ -16899,7 +16938,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A645">
         <v>2025</v>
       </c>
@@ -16910,7 +16949,7 @@
         <v>8</v>
       </c>
       <c r="D645" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E645">
         <v>17</v>
@@ -16922,7 +16961,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A646">
         <v>2025</v>
       </c>
@@ -16933,7 +16972,7 @@
         <v>8</v>
       </c>
       <c r="D646" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E646">
         <v>18</v>
@@ -16945,7 +16984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A647">
         <v>2025</v>
       </c>
@@ -16956,7 +16995,7 @@
         <v>8</v>
       </c>
       <c r="D647" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E647">
         <v>19</v>
@@ -16968,7 +17007,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A648">
         <v>2025</v>
       </c>
@@ -16979,7 +17018,7 @@
         <v>8</v>
       </c>
       <c r="D648" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E648">
         <v>20</v>
@@ -16991,7 +17030,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A649">
         <v>2025</v>
       </c>
@@ -17014,7 +17053,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A650">
         <v>2025</v>
       </c>
@@ -17025,7 +17064,7 @@
         <v>8</v>
       </c>
       <c r="D650" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E650">
         <v>22</v>
@@ -17037,7 +17076,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A651">
         <v>2025</v>
       </c>
@@ -17048,7 +17087,7 @@
         <v>8</v>
       </c>
       <c r="D651" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E651">
         <v>23</v>
@@ -17060,7 +17099,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A652">
         <v>2025</v>
       </c>
@@ -17071,7 +17110,7 @@
         <v>8</v>
       </c>
       <c r="D652" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E652">
         <v>24</v>
@@ -17083,7 +17122,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A653">
         <v>2025</v>
       </c>
@@ -17094,7 +17133,7 @@
         <v>8</v>
       </c>
       <c r="D653" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E653">
         <v>25</v>
@@ -17106,7 +17145,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A654">
         <v>2025</v>
       </c>
@@ -17117,7 +17156,7 @@
         <v>8</v>
       </c>
       <c r="D654" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E654">
         <v>26</v>
@@ -17129,7 +17168,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A655">
         <v>2025</v>
       </c>
@@ -17140,7 +17179,7 @@
         <v>8</v>
       </c>
       <c r="D655" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E655">
         <v>27</v>
@@ -17152,7 +17191,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A656">
         <v>2025</v>
       </c>
@@ -17163,7 +17202,7 @@
         <v>8</v>
       </c>
       <c r="D656" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E656">
         <v>28</v>
@@ -17209,7 +17248,7 @@
         <v>33</v>
       </c>
       <c r="D658" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E658">
         <v>1</v>
@@ -17261,7 +17300,7 @@
         <v>33</v>
       </c>
       <c r="D660" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E660">
         <v>3</v>
@@ -17313,7 +17352,7 @@
         <v>33</v>
       </c>
       <c r="D662" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E662">
         <v>5</v>
@@ -17339,7 +17378,7 @@
         <v>33</v>
       </c>
       <c r="D663" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E663">
         <v>6</v>
@@ -17365,7 +17404,7 @@
         <v>33</v>
       </c>
       <c r="D664" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E664">
         <v>7</v>
@@ -17443,7 +17482,7 @@
         <v>33</v>
       </c>
       <c r="D667" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E667">
         <v>10</v>
@@ -17588,7 +17627,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A673">
         <v>2025</v>
       </c>
@@ -17614,7 +17653,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A674">
         <v>2025</v>
       </c>
@@ -17625,7 +17664,7 @@
         <v>34</v>
       </c>
       <c r="D674" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E674">
         <v>2</v>
@@ -17640,7 +17679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A675">
         <v>2025</v>
       </c>
@@ -17651,7 +17690,7 @@
         <v>34</v>
       </c>
       <c r="D675" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E675">
         <v>3</v>
@@ -17666,7 +17705,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A676">
         <v>2025</v>
       </c>
@@ -17692,7 +17731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A677">
         <v>2025</v>
       </c>
@@ -17703,7 +17742,7 @@
         <v>34</v>
       </c>
       <c r="D677" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E677">
         <v>5</v>
@@ -17718,7 +17757,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A678">
         <v>2025</v>
       </c>
@@ -17729,25 +17768,22 @@
         <v>34</v>
       </c>
       <c r="D678" t="s">
-        <v>146</v>
-      </c>
-      <c r="E678" t="s">
-        <v>147</v>
+        <v>175</v>
+      </c>
+      <c r="E678">
+        <v>6</v>
       </c>
       <c r="F678">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G678">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H678">
-        <v>8</v>
-      </c>
-      <c r="I678">
         <v>10</v>
       </c>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A679">
         <v>2025</v>
       </c>
@@ -17773,7 +17809,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A680">
         <v>2025</v>
       </c>
@@ -17799,7 +17835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A681">
         <v>2025</v>
       </c>
@@ -17825,7 +17861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A682">
         <v>2025</v>
       </c>
@@ -17836,7 +17872,7 @@
         <v>34</v>
       </c>
       <c r="D682" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E682">
         <v>10</v>
@@ -17851,7 +17887,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A683">
         <v>2025</v>
       </c>
@@ -17862,7 +17898,7 @@
         <v>34</v>
       </c>
       <c r="D683" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E683">
         <v>11</v>
@@ -17877,7 +17913,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A684">
         <v>2025</v>
       </c>
@@ -17903,7 +17939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A685">
         <v>2025</v>
       </c>
@@ -17929,7 +17965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A686">
         <v>2025</v>
       </c>
@@ -17955,7 +17991,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A687">
         <v>2025</v>
       </c>
@@ -17981,7 +18017,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A688">
         <v>2025</v>
       </c>
@@ -18044,7 +18080,7 @@
         <v>35</v>
       </c>
       <c r="D690" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E690">
         <v>4</v>
@@ -18070,7 +18106,7 @@
         <v>35</v>
       </c>
       <c r="D691" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E691">
         <v>5</v>
@@ -18096,7 +18132,7 @@
         <v>35</v>
       </c>
       <c r="D692" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E692">
         <v>6</v>
@@ -18122,7 +18158,7 @@
         <v>35</v>
       </c>
       <c r="D693" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E693">
         <v>7</v>
@@ -18252,7 +18288,7 @@
         <v>35</v>
       </c>
       <c r="D698" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E698">
         <v>12</v>
@@ -18356,7 +18392,7 @@
         <v>35</v>
       </c>
       <c r="D702" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E702">
         <v>16</v>
@@ -18408,7 +18444,7 @@
         <v>35</v>
       </c>
       <c r="D704" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E704">
         <v>18</v>
@@ -18423,7 +18459,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A705">
         <v>2025</v>
       </c>
@@ -18449,7 +18485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A706">
         <v>2025</v>
       </c>
@@ -18460,7 +18496,7 @@
         <v>35</v>
       </c>
       <c r="D706" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E706">
         <v>20</v>
@@ -18475,7 +18511,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A707">
         <v>2025</v>
       </c>
@@ -18501,7 +18537,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A708">
         <v>2025</v>
       </c>
@@ -18527,7 +18563,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A709">
         <v>2025</v>
       </c>
@@ -18538,7 +18574,7 @@
         <v>35</v>
       </c>
       <c r="D709" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E709">
         <v>23</v>
@@ -18553,7 +18589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A710">
         <v>2025</v>
       </c>
@@ -18564,7 +18600,7 @@
         <v>35</v>
       </c>
       <c r="D710" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E710">
         <v>24</v>
@@ -18579,7 +18615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A711">
         <v>2025</v>
       </c>
@@ -18590,7 +18626,7 @@
         <v>35</v>
       </c>
       <c r="D711" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E711">
         <v>25</v>
@@ -18605,7 +18641,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A712">
         <v>2025</v>
       </c>
@@ -18616,25 +18652,22 @@
         <v>35</v>
       </c>
       <c r="D712" t="s">
-        <v>146</v>
-      </c>
-      <c r="E712" t="s">
-        <v>147</v>
+        <v>175</v>
+      </c>
+      <c r="E712">
+        <v>26</v>
       </c>
       <c r="F712">
         <v>26</v>
       </c>
       <c r="G712">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H712">
-        <v>20</v>
-      </c>
-      <c r="I712">
         <v>17</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A713">
         <v>2025</v>
       </c>
@@ -18645,7 +18678,7 @@
         <v>35</v>
       </c>
       <c r="D713" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E713">
         <v>1</v>
@@ -18660,7 +18693,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A714">
         <v>2025</v>
       </c>
@@ -18686,7 +18719,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A715">
         <v>2025</v>
       </c>
@@ -18712,7 +18745,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A716">
         <v>2025</v>
       </c>
@@ -18723,7 +18756,7 @@
         <v>35</v>
       </c>
       <c r="D716" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E716">
         <v>4</v>
@@ -18738,7 +18771,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A717">
         <v>2025</v>
       </c>
@@ -18749,7 +18782,7 @@
         <v>35</v>
       </c>
       <c r="D717" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E717">
         <v>5</v>
@@ -18764,7 +18797,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A718">
         <v>2025</v>
       </c>
@@ -18790,7 +18823,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A719">
         <v>2025</v>
       </c>
@@ -18801,7 +18834,7 @@
         <v>35</v>
       </c>
       <c r="D719" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E719">
         <v>7</v>
@@ -18816,7 +18849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A720">
         <v>2025</v>
       </c>
@@ -18842,7 +18875,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A721">
         <v>2025</v>
       </c>
@@ -18853,7 +18886,7 @@
         <v>35</v>
       </c>
       <c r="D721" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E721">
         <v>9</v>
@@ -18868,7 +18901,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A722">
         <v>2025</v>
       </c>
@@ -18879,7 +18912,7 @@
         <v>35</v>
       </c>
       <c r="D722" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E722">
         <v>10</v>
@@ -18894,7 +18927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A723">
         <v>2025</v>
       </c>
@@ -18920,7 +18953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A724">
         <v>2025</v>
       </c>
@@ -18946,7 +18979,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A725">
         <v>2025</v>
       </c>
@@ -18957,7 +18990,7 @@
         <v>35</v>
       </c>
       <c r="D725" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E725">
         <v>13</v>
@@ -18972,7 +19005,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A726">
         <v>2025</v>
       </c>
@@ -18998,7 +19031,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A727">
         <v>2025</v>
       </c>
@@ -19024,7 +19057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A728">
         <v>2025</v>
       </c>
@@ -19050,7 +19083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A729">
         <v>2025</v>
       </c>
@@ -19076,7 +19109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A730">
         <v>2025</v>
       </c>
@@ -19102,7 +19135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A731">
         <v>2025</v>
       </c>
@@ -19128,7 +19161,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A732">
         <v>2025</v>
       </c>
@@ -19154,7 +19187,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A733">
         <v>2025</v>
       </c>
@@ -19165,7 +19198,7 @@
         <v>35</v>
       </c>
       <c r="D733" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E733">
         <v>21</v>
@@ -19180,7 +19213,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A734">
         <v>2025</v>
       </c>
@@ -19206,7 +19239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A735">
         <v>2025</v>
       </c>
@@ -19217,7 +19250,7 @@
         <v>35</v>
       </c>
       <c r="D735" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E735">
         <v>23</v>
@@ -19232,7 +19265,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A736">
         <v>2025</v>
       </c>
@@ -19243,21 +19276,18 @@
         <v>35</v>
       </c>
       <c r="D736" t="s">
-        <v>162</v>
-      </c>
-      <c r="E736" t="s">
-        <v>147</v>
+        <v>174</v>
+      </c>
+      <c r="E736">
+        <v>24</v>
       </c>
       <c r="F736">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G736">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H736">
-        <v>19</v>
-      </c>
-      <c r="I736">
         <v>16</v>
       </c>
     </row>
@@ -19324,7 +19354,7 @@
         <v>35</v>
       </c>
       <c r="D739" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E739">
         <v>27</v>
@@ -19376,7 +19406,7 @@
         <v>35</v>
       </c>
       <c r="D741" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E741">
         <v>29</v>
@@ -19386,6 +19416,2086 @@
       </c>
       <c r="G741">
         <v>18</v>
+      </c>
+    </row>
+    <row r="742" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A742">
+        <v>2018</v>
+      </c>
+      <c r="B742">
+        <v>1</v>
+      </c>
+      <c r="C742" t="s">
+        <v>8</v>
+      </c>
+      <c r="D742" t="s">
+        <v>67</v>
+      </c>
+      <c r="E742">
+        <v>1</v>
+      </c>
+      <c r="F742">
+        <v>20</v>
+      </c>
+      <c r="G742">
+        <v>11</v>
+      </c>
+      <c r="H742">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="743" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A743">
+        <v>2018</v>
+      </c>
+      <c r="B743">
+        <v>1</v>
+      </c>
+      <c r="C743" t="s">
+        <v>8</v>
+      </c>
+      <c r="D743" t="s">
+        <v>160</v>
+      </c>
+      <c r="E743">
+        <v>2</v>
+      </c>
+      <c r="F743">
+        <v>20</v>
+      </c>
+      <c r="G743">
+        <v>4</v>
+      </c>
+      <c r="H743">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="744" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A744">
+        <v>2018</v>
+      </c>
+      <c r="B744">
+        <v>1</v>
+      </c>
+      <c r="C744" t="s">
+        <v>8</v>
+      </c>
+      <c r="D744" t="s">
+        <v>132</v>
+      </c>
+      <c r="E744">
+        <v>3</v>
+      </c>
+      <c r="F744">
+        <v>20</v>
+      </c>
+      <c r="G744">
+        <v>2</v>
+      </c>
+      <c r="H744">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="745" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A745">
+        <v>2018</v>
+      </c>
+      <c r="B745">
+        <v>1</v>
+      </c>
+      <c r="C745" t="s">
+        <v>8</v>
+      </c>
+      <c r="D745" t="s">
+        <v>81</v>
+      </c>
+      <c r="E745">
+        <v>4</v>
+      </c>
+      <c r="F745">
+        <v>20</v>
+      </c>
+      <c r="G745">
+        <v>6</v>
+      </c>
+      <c r="H745">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="746" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A746">
+        <v>2018</v>
+      </c>
+      <c r="B746">
+        <v>1</v>
+      </c>
+      <c r="C746" t="s">
+        <v>8</v>
+      </c>
+      <c r="D746" t="s">
+        <v>161</v>
+      </c>
+      <c r="E746">
+        <v>5</v>
+      </c>
+      <c r="F746">
+        <v>20</v>
+      </c>
+      <c r="G746">
+        <v>7</v>
+      </c>
+      <c r="H746">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="747" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A747">
+        <v>2018</v>
+      </c>
+      <c r="B747">
+        <v>1</v>
+      </c>
+      <c r="C747" t="s">
+        <v>8</v>
+      </c>
+      <c r="D747" t="s">
+        <v>162</v>
+      </c>
+      <c r="E747">
+        <v>6</v>
+      </c>
+      <c r="F747">
+        <v>20</v>
+      </c>
+      <c r="G747">
+        <v>1</v>
+      </c>
+      <c r="H747">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="748" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A748">
+        <v>2018</v>
+      </c>
+      <c r="B748">
+        <v>1</v>
+      </c>
+      <c r="C748" t="s">
+        <v>8</v>
+      </c>
+      <c r="D748" t="s">
+        <v>163</v>
+      </c>
+      <c r="E748">
+        <v>7</v>
+      </c>
+      <c r="F748">
+        <v>20</v>
+      </c>
+      <c r="G748">
+        <v>13</v>
+      </c>
+      <c r="H748">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="749" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A749">
+        <v>2018</v>
+      </c>
+      <c r="B749">
+        <v>1</v>
+      </c>
+      <c r="C749" t="s">
+        <v>8</v>
+      </c>
+      <c r="D749" t="s">
+        <v>164</v>
+      </c>
+      <c r="E749">
+        <v>8</v>
+      </c>
+      <c r="F749">
+        <v>20</v>
+      </c>
+      <c r="G749">
+        <v>3</v>
+      </c>
+      <c r="H749">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="750" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A750">
+        <v>2018</v>
+      </c>
+      <c r="B750">
+        <v>1</v>
+      </c>
+      <c r="C750" t="s">
+        <v>8</v>
+      </c>
+      <c r="D750" t="s">
+        <v>72</v>
+      </c>
+      <c r="E750">
+        <v>9</v>
+      </c>
+      <c r="F750">
+        <v>20</v>
+      </c>
+      <c r="G750">
+        <v>8</v>
+      </c>
+      <c r="H750">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="751" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A751">
+        <v>2018</v>
+      </c>
+      <c r="B751">
+        <v>1</v>
+      </c>
+      <c r="C751" t="s">
+        <v>8</v>
+      </c>
+      <c r="D751" t="s">
+        <v>63</v>
+      </c>
+      <c r="E751">
+        <v>10</v>
+      </c>
+      <c r="F751">
+        <v>20</v>
+      </c>
+      <c r="G751">
+        <v>14</v>
+      </c>
+      <c r="H751">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="752" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A752">
+        <v>2018</v>
+      </c>
+      <c r="B752">
+        <v>1</v>
+      </c>
+      <c r="C752" t="s">
+        <v>8</v>
+      </c>
+      <c r="D752" t="s">
+        <v>165</v>
+      </c>
+      <c r="E752">
+        <v>11</v>
+      </c>
+      <c r="F752">
+        <v>20</v>
+      </c>
+      <c r="G752">
+        <v>15</v>
+      </c>
+      <c r="H752">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="753" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A753">
+        <v>2018</v>
+      </c>
+      <c r="B753">
+        <v>1</v>
+      </c>
+      <c r="C753" t="s">
+        <v>8</v>
+      </c>
+      <c r="D753" t="s">
+        <v>166</v>
+      </c>
+      <c r="E753">
+        <v>12</v>
+      </c>
+      <c r="F753">
+        <v>20</v>
+      </c>
+      <c r="G753">
+        <v>20</v>
+      </c>
+      <c r="H753">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="754" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A754">
+        <v>2018</v>
+      </c>
+      <c r="B754">
+        <v>1</v>
+      </c>
+      <c r="C754" t="s">
+        <v>8</v>
+      </c>
+      <c r="D754" t="s">
+        <v>167</v>
+      </c>
+      <c r="E754">
+        <v>13</v>
+      </c>
+      <c r="F754">
+        <v>20</v>
+      </c>
+      <c r="G754">
+        <v>10</v>
+      </c>
+      <c r="H754">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="755" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A755">
+        <v>2018</v>
+      </c>
+      <c r="B755">
+        <v>1</v>
+      </c>
+      <c r="C755" t="s">
+        <v>8</v>
+      </c>
+      <c r="D755" t="s">
+        <v>168</v>
+      </c>
+      <c r="E755">
+        <v>14</v>
+      </c>
+      <c r="F755">
+        <v>20</v>
+      </c>
+      <c r="G755">
+        <v>12</v>
+      </c>
+      <c r="H755">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="756" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A756">
+        <v>2018</v>
+      </c>
+      <c r="B756">
+        <v>1</v>
+      </c>
+      <c r="C756" t="s">
+        <v>8</v>
+      </c>
+      <c r="D756" t="s">
+        <v>169</v>
+      </c>
+      <c r="E756">
+        <v>15</v>
+      </c>
+      <c r="F756">
+        <v>20</v>
+      </c>
+      <c r="G756">
+        <v>5</v>
+      </c>
+      <c r="H756">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="757" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A757">
+        <v>2018</v>
+      </c>
+      <c r="B757">
+        <v>1</v>
+      </c>
+      <c r="C757" t="s">
+        <v>8</v>
+      </c>
+      <c r="D757" t="s">
+        <v>170</v>
+      </c>
+      <c r="E757">
+        <v>16</v>
+      </c>
+      <c r="F757">
+        <v>20</v>
+      </c>
+      <c r="G757">
+        <v>17</v>
+      </c>
+      <c r="H757">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="758" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A758">
+        <v>2018</v>
+      </c>
+      <c r="B758">
+        <v>1</v>
+      </c>
+      <c r="C758" t="s">
+        <v>8</v>
+      </c>
+      <c r="D758" t="s">
+        <v>171</v>
+      </c>
+      <c r="E758">
+        <v>17</v>
+      </c>
+      <c r="F758">
+        <v>20</v>
+      </c>
+      <c r="G758">
+        <v>19</v>
+      </c>
+      <c r="H758">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="759" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A759">
+        <v>2018</v>
+      </c>
+      <c r="B759">
+        <v>1</v>
+      </c>
+      <c r="C759" t="s">
+        <v>8</v>
+      </c>
+      <c r="D759" t="s">
+        <v>172</v>
+      </c>
+      <c r="E759">
+        <v>18</v>
+      </c>
+      <c r="F759">
+        <v>20</v>
+      </c>
+      <c r="G759">
+        <v>16</v>
+      </c>
+      <c r="H759">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="760" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A760">
+        <v>2018</v>
+      </c>
+      <c r="B760">
+        <v>1</v>
+      </c>
+      <c r="C760" t="s">
+        <v>8</v>
+      </c>
+      <c r="D760" t="s">
+        <v>173</v>
+      </c>
+      <c r="E760">
+        <v>19</v>
+      </c>
+      <c r="F760">
+        <v>20</v>
+      </c>
+      <c r="G760">
+        <v>9</v>
+      </c>
+      <c r="H760">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="761" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A761">
+        <v>2018</v>
+      </c>
+      <c r="B761">
+        <v>1</v>
+      </c>
+      <c r="C761" t="s">
+        <v>8</v>
+      </c>
+      <c r="D761" t="s">
+        <v>41</v>
+      </c>
+      <c r="E761">
+        <v>20</v>
+      </c>
+      <c r="F761">
+        <v>20</v>
+      </c>
+      <c r="G761">
+        <v>18</v>
+      </c>
+      <c r="H761">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="762" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A762">
+        <v>2018</v>
+      </c>
+      <c r="B762">
+        <v>2</v>
+      </c>
+      <c r="C762" t="s">
+        <v>33</v>
+      </c>
+      <c r="D762" t="s">
+        <v>41</v>
+      </c>
+      <c r="E762">
+        <v>1</v>
+      </c>
+      <c r="F762">
+        <v>10</v>
+      </c>
+      <c r="G762">
+        <v>8</v>
+      </c>
+      <c r="H762">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="763" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A763">
+        <v>2018</v>
+      </c>
+      <c r="B763">
+        <v>2</v>
+      </c>
+      <c r="C763" t="s">
+        <v>33</v>
+      </c>
+      <c r="D763" t="s">
+        <v>171</v>
+      </c>
+      <c r="E763">
+        <v>2</v>
+      </c>
+      <c r="F763">
+        <v>10</v>
+      </c>
+      <c r="G763">
+        <v>7</v>
+      </c>
+      <c r="H763">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="764" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A764">
+        <v>2018</v>
+      </c>
+      <c r="B764">
+        <v>2</v>
+      </c>
+      <c r="C764" t="s">
+        <v>33</v>
+      </c>
+      <c r="D764" t="s">
+        <v>170</v>
+      </c>
+      <c r="E764">
+        <v>3</v>
+      </c>
+      <c r="F764">
+        <v>10</v>
+      </c>
+      <c r="G764">
+        <v>5</v>
+      </c>
+      <c r="H764">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="765" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A765">
+        <v>2018</v>
+      </c>
+      <c r="B765">
+        <v>2</v>
+      </c>
+      <c r="C765" t="s">
+        <v>33</v>
+      </c>
+      <c r="D765" t="s">
+        <v>166</v>
+      </c>
+      <c r="E765">
+        <v>4</v>
+      </c>
+      <c r="F765">
+        <v>10</v>
+      </c>
+      <c r="G765">
+        <v>10</v>
+      </c>
+      <c r="H765">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="766" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A766">
+        <v>2018</v>
+      </c>
+      <c r="B766">
+        <v>2</v>
+      </c>
+      <c r="C766" t="s">
+        <v>33</v>
+      </c>
+      <c r="D766" t="s">
+        <v>161</v>
+      </c>
+      <c r="E766">
+        <v>5</v>
+      </c>
+      <c r="F766">
+        <v>10</v>
+      </c>
+      <c r="G766">
+        <v>3</v>
+      </c>
+      <c r="H766">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="767" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A767">
+        <v>2018</v>
+      </c>
+      <c r="B767">
+        <v>2</v>
+      </c>
+      <c r="C767" t="s">
+        <v>33</v>
+      </c>
+      <c r="D767" t="s">
+        <v>168</v>
+      </c>
+      <c r="E767">
+        <v>6</v>
+      </c>
+      <c r="F767">
+        <v>10</v>
+      </c>
+      <c r="G767">
+        <v>4</v>
+      </c>
+      <c r="H767">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="768" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A768">
+        <v>2018</v>
+      </c>
+      <c r="B768">
+        <v>2</v>
+      </c>
+      <c r="C768" t="s">
+        <v>33</v>
+      </c>
+      <c r="D768" t="s">
+        <v>160</v>
+      </c>
+      <c r="E768">
+        <v>7</v>
+      </c>
+      <c r="F768">
+        <v>10</v>
+      </c>
+      <c r="G768">
+        <v>2</v>
+      </c>
+      <c r="H768">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="769" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A769">
+        <v>2018</v>
+      </c>
+      <c r="B769">
+        <v>2</v>
+      </c>
+      <c r="C769" t="s">
+        <v>33</v>
+      </c>
+      <c r="D769" t="s">
+        <v>172</v>
+      </c>
+      <c r="E769">
+        <v>8</v>
+      </c>
+      <c r="F769">
+        <v>10</v>
+      </c>
+      <c r="G769">
+        <v>6</v>
+      </c>
+      <c r="H769">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="770" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A770">
+        <v>2018</v>
+      </c>
+      <c r="B770">
+        <v>2</v>
+      </c>
+      <c r="C770" t="s">
+        <v>33</v>
+      </c>
+      <c r="D770" t="s">
+        <v>67</v>
+      </c>
+      <c r="E770">
+        <v>9</v>
+      </c>
+      <c r="F770">
+        <v>10</v>
+      </c>
+      <c r="G770">
+        <v>1</v>
+      </c>
+      <c r="H770">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="771" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A771">
+        <v>2018</v>
+      </c>
+      <c r="B771">
+        <v>2</v>
+      </c>
+      <c r="C771" t="s">
+        <v>33</v>
+      </c>
+      <c r="D771" t="s">
+        <v>165</v>
+      </c>
+      <c r="E771">
+        <v>10</v>
+      </c>
+      <c r="F771">
+        <v>10</v>
+      </c>
+      <c r="G771">
+        <v>9</v>
+      </c>
+      <c r="H771">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="772" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A772">
+        <v>2018</v>
+      </c>
+      <c r="B772">
+        <v>3</v>
+      </c>
+      <c r="C772" t="s">
+        <v>34</v>
+      </c>
+      <c r="D772" t="s">
+        <v>167</v>
+      </c>
+      <c r="E772">
+        <v>1</v>
+      </c>
+      <c r="F772">
+        <v>10</v>
+      </c>
+      <c r="G772">
+        <v>8</v>
+      </c>
+      <c r="H772">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="773" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A773">
+        <v>2018</v>
+      </c>
+      <c r="B773">
+        <v>3</v>
+      </c>
+      <c r="C773" t="s">
+        <v>34</v>
+      </c>
+      <c r="D773" t="s">
+        <v>72</v>
+      </c>
+      <c r="E773">
+        <v>2</v>
+      </c>
+      <c r="F773">
+        <v>10</v>
+      </c>
+      <c r="G773">
+        <v>4</v>
+      </c>
+      <c r="H773">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="774" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A774">
+        <v>2018</v>
+      </c>
+      <c r="B774">
+        <v>3</v>
+      </c>
+      <c r="C774" t="s">
+        <v>34</v>
+      </c>
+      <c r="D774" t="s">
+        <v>169</v>
+      </c>
+      <c r="E774">
+        <v>3</v>
+      </c>
+      <c r="F774">
+        <v>10</v>
+      </c>
+      <c r="G774">
+        <v>2</v>
+      </c>
+      <c r="H774">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="775" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A775">
+        <v>2018</v>
+      </c>
+      <c r="B775">
+        <v>3</v>
+      </c>
+      <c r="C775" t="s">
+        <v>34</v>
+      </c>
+      <c r="D775" t="s">
+        <v>173</v>
+      </c>
+      <c r="E775">
+        <v>4</v>
+      </c>
+      <c r="F775">
+        <v>10</v>
+      </c>
+      <c r="G775">
+        <v>6</v>
+      </c>
+      <c r="H775">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="776" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A776">
+        <v>2018</v>
+      </c>
+      <c r="B776">
+        <v>3</v>
+      </c>
+      <c r="C776" t="s">
+        <v>34</v>
+      </c>
+      <c r="D776" t="s">
+        <v>81</v>
+      </c>
+      <c r="E776">
+        <v>5</v>
+      </c>
+      <c r="F776">
+        <v>10</v>
+      </c>
+      <c r="G776">
+        <v>5</v>
+      </c>
+      <c r="H776">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="777" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A777">
+        <v>2018</v>
+      </c>
+      <c r="B777">
+        <v>3</v>
+      </c>
+      <c r="C777" t="s">
+        <v>34</v>
+      </c>
+      <c r="D777" t="s">
+        <v>164</v>
+      </c>
+      <c r="E777">
+        <v>6</v>
+      </c>
+      <c r="F777">
+        <v>10</v>
+      </c>
+      <c r="G777">
+        <v>7</v>
+      </c>
+      <c r="H777">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="778" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A778">
+        <v>2018</v>
+      </c>
+      <c r="B778">
+        <v>3</v>
+      </c>
+      <c r="C778" t="s">
+        <v>34</v>
+      </c>
+      <c r="D778" t="s">
+        <v>162</v>
+      </c>
+      <c r="E778">
+        <v>7</v>
+      </c>
+      <c r="F778">
+        <v>10</v>
+      </c>
+      <c r="G778">
+        <v>0</v>
+      </c>
+      <c r="H778">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="779" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A779">
+        <v>2018</v>
+      </c>
+      <c r="B779">
+        <v>3</v>
+      </c>
+      <c r="C779" t="s">
+        <v>34</v>
+      </c>
+      <c r="D779" t="s">
+        <v>63</v>
+      </c>
+      <c r="E779">
+        <v>8</v>
+      </c>
+      <c r="F779">
+        <v>10</v>
+      </c>
+      <c r="G779">
+        <v>9</v>
+      </c>
+      <c r="H779">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="780" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A780">
+        <v>2018</v>
+      </c>
+      <c r="B780">
+        <v>3</v>
+      </c>
+      <c r="C780" t="s">
+        <v>34</v>
+      </c>
+      <c r="D780" t="s">
+        <v>132</v>
+      </c>
+      <c r="E780">
+        <v>9</v>
+      </c>
+      <c r="F780">
+        <v>10</v>
+      </c>
+      <c r="G780">
+        <v>3</v>
+      </c>
+      <c r="H780">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="781" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A781">
+        <v>2018</v>
+      </c>
+      <c r="B781">
+        <v>3</v>
+      </c>
+      <c r="C781" t="s">
+        <v>34</v>
+      </c>
+      <c r="D781" t="s">
+        <v>163</v>
+      </c>
+      <c r="E781">
+        <v>10</v>
+      </c>
+      <c r="F781">
+        <v>10</v>
+      </c>
+      <c r="G781">
+        <v>10</v>
+      </c>
+      <c r="H781">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="782" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A782">
+        <v>2018</v>
+      </c>
+      <c r="B782">
+        <v>4</v>
+      </c>
+      <c r="C782" t="s">
+        <v>35</v>
+      </c>
+      <c r="D782" t="s">
+        <v>172</v>
+      </c>
+      <c r="E782">
+        <v>1</v>
+      </c>
+      <c r="F782">
+        <v>20</v>
+      </c>
+      <c r="G782">
+        <v>7</v>
+      </c>
+      <c r="H782">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="783" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A783">
+        <v>2018</v>
+      </c>
+      <c r="B783">
+        <v>4</v>
+      </c>
+      <c r="C783" t="s">
+        <v>35</v>
+      </c>
+      <c r="D783" t="s">
+        <v>41</v>
+      </c>
+      <c r="E783">
+        <v>2</v>
+      </c>
+      <c r="F783">
+        <v>20</v>
+      </c>
+      <c r="G783">
+        <v>15</v>
+      </c>
+      <c r="H783">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="784" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A784">
+        <v>2018</v>
+      </c>
+      <c r="B784">
+        <v>4</v>
+      </c>
+      <c r="C784" t="s">
+        <v>35</v>
+      </c>
+      <c r="D784" t="s">
+        <v>63</v>
+      </c>
+      <c r="E784">
+        <v>3</v>
+      </c>
+      <c r="F784">
+        <v>20</v>
+      </c>
+      <c r="G784">
+        <v>12</v>
+      </c>
+      <c r="H784">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="785" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A785">
+        <v>2018</v>
+      </c>
+      <c r="B785">
+        <v>4</v>
+      </c>
+      <c r="C785" t="s">
+        <v>35</v>
+      </c>
+      <c r="D785" t="s">
+        <v>163</v>
+      </c>
+      <c r="E785">
+        <v>4</v>
+      </c>
+      <c r="F785">
+        <v>20</v>
+      </c>
+      <c r="G785">
+        <v>18</v>
+      </c>
+      <c r="H785">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="786" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A786">
+        <v>2018</v>
+      </c>
+      <c r="B786">
+        <v>4</v>
+      </c>
+      <c r="C786" t="s">
+        <v>35</v>
+      </c>
+      <c r="D786" t="s">
+        <v>67</v>
+      </c>
+      <c r="E786">
+        <v>5</v>
+      </c>
+      <c r="F786">
+        <v>20</v>
+      </c>
+      <c r="G786">
+        <v>2</v>
+      </c>
+      <c r="H786">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="787" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A787">
+        <v>2018</v>
+      </c>
+      <c r="B787">
+        <v>4</v>
+      </c>
+      <c r="C787" t="s">
+        <v>35</v>
+      </c>
+      <c r="D787" t="s">
+        <v>72</v>
+      </c>
+      <c r="E787">
+        <v>6</v>
+      </c>
+      <c r="F787">
+        <v>20</v>
+      </c>
+      <c r="G787">
+        <v>3</v>
+      </c>
+      <c r="H787">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="788" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A788">
+        <v>2018</v>
+      </c>
+      <c r="B788">
+        <v>4</v>
+      </c>
+      <c r="C788" t="s">
+        <v>35</v>
+      </c>
+      <c r="D788" t="s">
+        <v>81</v>
+      </c>
+      <c r="E788">
+        <v>7</v>
+      </c>
+      <c r="F788">
+        <v>20</v>
+      </c>
+      <c r="G788">
+        <v>5</v>
+      </c>
+      <c r="H788">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="789" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A789">
+        <v>2018</v>
+      </c>
+      <c r="B789">
+        <v>4</v>
+      </c>
+      <c r="C789" t="s">
+        <v>35</v>
+      </c>
+      <c r="D789" t="s">
+        <v>165</v>
+      </c>
+      <c r="E789">
+        <v>8</v>
+      </c>
+      <c r="F789">
+        <v>20</v>
+      </c>
+      <c r="G789">
+        <v>14</v>
+      </c>
+      <c r="H789">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="790" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A790">
+        <v>2018</v>
+      </c>
+      <c r="B790">
+        <v>4</v>
+      </c>
+      <c r="C790" t="s">
+        <v>35</v>
+      </c>
+      <c r="D790" t="s">
+        <v>161</v>
+      </c>
+      <c r="E790">
+        <v>9</v>
+      </c>
+      <c r="F790">
+        <v>20</v>
+      </c>
+      <c r="G790">
+        <v>8</v>
+      </c>
+      <c r="H790">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="791" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A791">
+        <v>2018</v>
+      </c>
+      <c r="B791">
+        <v>4</v>
+      </c>
+      <c r="C791" t="s">
+        <v>35</v>
+      </c>
+      <c r="D791" t="s">
+        <v>170</v>
+      </c>
+      <c r="E791">
+        <v>10</v>
+      </c>
+      <c r="F791">
+        <v>20</v>
+      </c>
+      <c r="G791">
+        <v>13</v>
+      </c>
+      <c r="H791">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="792" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A792">
+        <v>2018</v>
+      </c>
+      <c r="B792">
+        <v>4</v>
+      </c>
+      <c r="C792" t="s">
+        <v>35</v>
+      </c>
+      <c r="D792" t="s">
+        <v>164</v>
+      </c>
+      <c r="E792">
+        <v>11</v>
+      </c>
+      <c r="F792">
+        <v>20</v>
+      </c>
+      <c r="G792">
+        <v>11</v>
+      </c>
+      <c r="H792">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="793" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A793">
+        <v>2018</v>
+      </c>
+      <c r="B793">
+        <v>4</v>
+      </c>
+      <c r="C793" t="s">
+        <v>35</v>
+      </c>
+      <c r="D793" t="s">
+        <v>173</v>
+      </c>
+      <c r="E793">
+        <v>12</v>
+      </c>
+      <c r="F793">
+        <v>20</v>
+      </c>
+      <c r="G793">
+        <v>10</v>
+      </c>
+      <c r="H793">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="794" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A794">
+        <v>2018</v>
+      </c>
+      <c r="B794">
+        <v>4</v>
+      </c>
+      <c r="C794" t="s">
+        <v>35</v>
+      </c>
+      <c r="D794" t="s">
+        <v>162</v>
+      </c>
+      <c r="E794">
+        <v>13</v>
+      </c>
+      <c r="F794">
+        <v>20</v>
+      </c>
+      <c r="G794">
+        <v>1</v>
+      </c>
+      <c r="H794">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="795" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A795">
+        <v>2018</v>
+      </c>
+      <c r="B795">
+        <v>4</v>
+      </c>
+      <c r="C795" t="s">
+        <v>35</v>
+      </c>
+      <c r="D795" t="s">
+        <v>167</v>
+      </c>
+      <c r="E795">
+        <v>14</v>
+      </c>
+      <c r="F795">
+        <v>20</v>
+      </c>
+      <c r="G795">
+        <v>16</v>
+      </c>
+      <c r="H795">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="796" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A796">
+        <v>2018</v>
+      </c>
+      <c r="B796">
+        <v>4</v>
+      </c>
+      <c r="C796" t="s">
+        <v>35</v>
+      </c>
+      <c r="D796" t="s">
+        <v>160</v>
+      </c>
+      <c r="E796">
+        <v>15</v>
+      </c>
+      <c r="F796">
+        <v>20</v>
+      </c>
+      <c r="G796">
+        <v>9</v>
+      </c>
+      <c r="H796">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="797" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A797">
+        <v>2018</v>
+      </c>
+      <c r="B797">
+        <v>4</v>
+      </c>
+      <c r="C797" t="s">
+        <v>35</v>
+      </c>
+      <c r="D797" t="s">
+        <v>168</v>
+      </c>
+      <c r="E797">
+        <v>16</v>
+      </c>
+      <c r="F797">
+        <v>20</v>
+      </c>
+      <c r="G797">
+        <v>17</v>
+      </c>
+      <c r="H797">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="798" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A798">
+        <v>2018</v>
+      </c>
+      <c r="B798">
+        <v>4</v>
+      </c>
+      <c r="C798" t="s">
+        <v>35</v>
+      </c>
+      <c r="D798" t="s">
+        <v>132</v>
+      </c>
+      <c r="E798">
+        <v>17</v>
+      </c>
+      <c r="F798">
+        <v>20</v>
+      </c>
+      <c r="G798">
+        <v>5</v>
+      </c>
+      <c r="H798">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="799" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A799">
+        <v>2018</v>
+      </c>
+      <c r="B799">
+        <v>4</v>
+      </c>
+      <c r="C799" t="s">
+        <v>35</v>
+      </c>
+      <c r="D799" t="s">
+        <v>169</v>
+      </c>
+      <c r="E799">
+        <v>18</v>
+      </c>
+      <c r="F799">
+        <v>20</v>
+      </c>
+      <c r="G799">
+        <v>6</v>
+      </c>
+      <c r="H799">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="800" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A800">
+        <v>2018</v>
+      </c>
+      <c r="B800">
+        <v>4</v>
+      </c>
+      <c r="C800" t="s">
+        <v>35</v>
+      </c>
+      <c r="D800" t="s">
+        <v>171</v>
+      </c>
+      <c r="E800">
+        <v>19</v>
+      </c>
+      <c r="F800">
+        <v>20</v>
+      </c>
+      <c r="G800">
+        <v>19</v>
+      </c>
+      <c r="H800">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="801" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A801">
+        <v>2018</v>
+      </c>
+      <c r="B801">
+        <v>4</v>
+      </c>
+      <c r="C801" t="s">
+        <v>35</v>
+      </c>
+      <c r="D801" t="s">
+        <v>166</v>
+      </c>
+      <c r="E801">
+        <v>20</v>
+      </c>
+      <c r="F801">
+        <v>20</v>
+      </c>
+      <c r="G801">
+        <v>20</v>
+      </c>
+      <c r="H801">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="802" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A802">
+        <v>2018</v>
+      </c>
+      <c r="B802">
+        <v>5</v>
+      </c>
+      <c r="C802" t="s">
+        <v>36</v>
+      </c>
+      <c r="D802" t="s">
+        <v>169</v>
+      </c>
+      <c r="E802">
+        <v>1</v>
+      </c>
+      <c r="F802">
+        <v>20</v>
+      </c>
+      <c r="G802">
+        <v>4</v>
+      </c>
+      <c r="H802">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="803" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A803">
+        <v>2018</v>
+      </c>
+      <c r="B803">
+        <v>5</v>
+      </c>
+      <c r="C803" t="s">
+        <v>36</v>
+      </c>
+      <c r="D803" t="s">
+        <v>168</v>
+      </c>
+      <c r="E803">
+        <v>2</v>
+      </c>
+      <c r="F803">
+        <v>20</v>
+      </c>
+      <c r="G803">
+        <v>13</v>
+      </c>
+      <c r="H803">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="804" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A804">
+        <v>2018</v>
+      </c>
+      <c r="B804">
+        <v>5</v>
+      </c>
+      <c r="C804" t="s">
+        <v>36</v>
+      </c>
+      <c r="D804" t="s">
+        <v>132</v>
+      </c>
+      <c r="E804">
+        <v>3</v>
+      </c>
+      <c r="F804">
+        <v>20</v>
+      </c>
+      <c r="G804">
+        <v>5</v>
+      </c>
+      <c r="H804">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="805" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A805">
+        <v>2018</v>
+      </c>
+      <c r="B805">
+        <v>5</v>
+      </c>
+      <c r="C805" t="s">
+        <v>36</v>
+      </c>
+      <c r="D805" t="s">
+        <v>166</v>
+      </c>
+      <c r="E805">
+        <v>4</v>
+      </c>
+      <c r="F805">
+        <v>20</v>
+      </c>
+      <c r="G805">
+        <v>19</v>
+      </c>
+      <c r="H805">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="806" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A806">
+        <v>2018</v>
+      </c>
+      <c r="B806">
+        <v>5</v>
+      </c>
+      <c r="C806" t="s">
+        <v>36</v>
+      </c>
+      <c r="D806" t="s">
+        <v>160</v>
+      </c>
+      <c r="E806">
+        <v>5</v>
+      </c>
+      <c r="F806">
+        <v>20</v>
+      </c>
+      <c r="G806">
+        <v>7</v>
+      </c>
+      <c r="H806">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="807" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A807">
+        <v>2018</v>
+      </c>
+      <c r="B807">
+        <v>5</v>
+      </c>
+      <c r="C807" t="s">
+        <v>36</v>
+      </c>
+      <c r="D807" t="s">
+        <v>81</v>
+      </c>
+      <c r="E807">
+        <v>6</v>
+      </c>
+      <c r="F807">
+        <v>20</v>
+      </c>
+      <c r="G807">
+        <v>6</v>
+      </c>
+      <c r="H807">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="808" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A808">
+        <v>2018</v>
+      </c>
+      <c r="B808">
+        <v>5</v>
+      </c>
+      <c r="C808" t="s">
+        <v>36</v>
+      </c>
+      <c r="D808" t="s">
+        <v>67</v>
+      </c>
+      <c r="E808">
+        <v>7</v>
+      </c>
+      <c r="F808">
+        <v>20</v>
+      </c>
+      <c r="G808">
+        <v>3</v>
+      </c>
+      <c r="H808">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="809" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A809">
+        <v>2018</v>
+      </c>
+      <c r="B809">
+        <v>5</v>
+      </c>
+      <c r="C809" t="s">
+        <v>36</v>
+      </c>
+      <c r="D809" t="s">
+        <v>172</v>
+      </c>
+      <c r="E809">
+        <v>8</v>
+      </c>
+      <c r="F809">
+        <v>20</v>
+      </c>
+      <c r="G809">
+        <v>17</v>
+      </c>
+      <c r="H809">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="810" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A810">
+        <v>2018</v>
+      </c>
+      <c r="B810">
+        <v>5</v>
+      </c>
+      <c r="C810" t="s">
+        <v>36</v>
+      </c>
+      <c r="D810" t="s">
+        <v>165</v>
+      </c>
+      <c r="E810">
+        <v>9</v>
+      </c>
+      <c r="F810">
+        <v>20</v>
+      </c>
+      <c r="G810">
+        <v>15</v>
+      </c>
+      <c r="H810">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="811" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A811">
+        <v>2018</v>
+      </c>
+      <c r="B811">
+        <v>5</v>
+      </c>
+      <c r="C811" t="s">
+        <v>36</v>
+      </c>
+      <c r="D811" t="s">
+        <v>161</v>
+      </c>
+      <c r="E811">
+        <v>10</v>
+      </c>
+      <c r="F811">
+        <v>20</v>
+      </c>
+      <c r="G811">
+        <v>8</v>
+      </c>
+      <c r="H811">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="812" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A812">
+        <v>2018</v>
+      </c>
+      <c r="B812">
+        <v>5</v>
+      </c>
+      <c r="C812" t="s">
+        <v>36</v>
+      </c>
+      <c r="D812" t="s">
+        <v>167</v>
+      </c>
+      <c r="E812">
+        <v>11</v>
+      </c>
+      <c r="F812">
+        <v>20</v>
+      </c>
+      <c r="G812">
+        <v>10</v>
+      </c>
+      <c r="H812">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="813" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A813">
+        <v>2018</v>
+      </c>
+      <c r="B813">
+        <v>5</v>
+      </c>
+      <c r="C813" t="s">
+        <v>36</v>
+      </c>
+      <c r="D813" t="s">
+        <v>72</v>
+      </c>
+      <c r="E813">
+        <v>12</v>
+      </c>
+      <c r="F813">
+        <v>20</v>
+      </c>
+      <c r="G813">
+        <v>2</v>
+      </c>
+      <c r="H813">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="814" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A814">
+        <v>2018</v>
+      </c>
+      <c r="B814">
+        <v>5</v>
+      </c>
+      <c r="C814" t="s">
+        <v>36</v>
+      </c>
+      <c r="D814" t="s">
+        <v>164</v>
+      </c>
+      <c r="E814">
+        <v>13</v>
+      </c>
+      <c r="F814">
+        <v>20</v>
+      </c>
+      <c r="G814">
+        <v>12</v>
+      </c>
+      <c r="H814">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="815" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A815">
+        <v>2018</v>
+      </c>
+      <c r="B815">
+        <v>5</v>
+      </c>
+      <c r="C815" t="s">
+        <v>36</v>
+      </c>
+      <c r="D815" t="s">
+        <v>170</v>
+      </c>
+      <c r="E815">
+        <v>14</v>
+      </c>
+      <c r="F815">
+        <v>20</v>
+      </c>
+      <c r="G815">
+        <v>9</v>
+      </c>
+      <c r="H815">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="816" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A816">
+        <v>2018</v>
+      </c>
+      <c r="B816">
+        <v>5</v>
+      </c>
+      <c r="C816" t="s">
+        <v>36</v>
+      </c>
+      <c r="D816" t="s">
+        <v>171</v>
+      </c>
+      <c r="E816">
+        <v>15</v>
+      </c>
+      <c r="F816">
+        <v>20</v>
+      </c>
+      <c r="G816">
+        <v>18</v>
+      </c>
+      <c r="H816">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="817" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A817">
+        <v>2018</v>
+      </c>
+      <c r="B817">
+        <v>5</v>
+      </c>
+      <c r="C817" t="s">
+        <v>36</v>
+      </c>
+      <c r="D817" t="s">
+        <v>63</v>
+      </c>
+      <c r="E817">
+        <v>16</v>
+      </c>
+      <c r="F817">
+        <v>20</v>
+      </c>
+      <c r="G817">
+        <v>16</v>
+      </c>
+      <c r="H817">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="818" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A818">
+        <v>2018</v>
+      </c>
+      <c r="B818">
+        <v>5</v>
+      </c>
+      <c r="C818" t="s">
+        <v>36</v>
+      </c>
+      <c r="D818" t="s">
+        <v>162</v>
+      </c>
+      <c r="E818">
+        <v>17</v>
+      </c>
+      <c r="F818">
+        <v>20</v>
+      </c>
+      <c r="G818">
+        <v>1</v>
+      </c>
+      <c r="H818">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="819" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A819">
+        <v>2018</v>
+      </c>
+      <c r="B819">
+        <v>5</v>
+      </c>
+      <c r="C819" t="s">
+        <v>36</v>
+      </c>
+      <c r="D819" t="s">
+        <v>163</v>
+      </c>
+      <c r="E819">
+        <v>18</v>
+      </c>
+      <c r="F819">
+        <v>20</v>
+      </c>
+      <c r="G819">
+        <v>20</v>
+      </c>
+      <c r="H819">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="820" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A820">
+        <v>2018</v>
+      </c>
+      <c r="B820">
+        <v>5</v>
+      </c>
+      <c r="C820" t="s">
+        <v>36</v>
+      </c>
+      <c r="D820" t="s">
+        <v>41</v>
+      </c>
+      <c r="E820">
+        <v>19</v>
+      </c>
+      <c r="F820">
+        <v>20</v>
+      </c>
+      <c r="G820">
+        <v>11</v>
+      </c>
+      <c r="H820">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="821" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A821">
+        <v>2018</v>
+      </c>
+      <c r="B821">
+        <v>5</v>
+      </c>
+      <c r="C821" t="s">
+        <v>36</v>
+      </c>
+      <c r="D821" t="s">
+        <v>173</v>
+      </c>
+      <c r="E821">
+        <v>20</v>
+      </c>
+      <c r="F821">
+        <v>20</v>
+      </c>
+      <c r="G821">
+        <v>14</v>
+      </c>
+      <c r="H821">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/dati_sremo/sanremo_dati_serate.xlsx
+++ b/dati_sremo/sanremo_dati_serate.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/umbertobertonelli/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E9978F-B887-444E-B5EC-561651833527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97626A6-3FC4-454B-9DA7-676C4857ED51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="39800" yWindow="6160" windowWidth="28040" windowHeight="17180" xr2:uid="{B4699A91-0234-EF40-A7DC-9F915DE8C013}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$H$941</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="194">
   <si>
     <t>year</t>
   </si>
@@ -565,6 +568,60 @@
   <si>
     <t>Shablo con Guè  Joshua e Tormento</t>
   </si>
+  <si>
+    <t>Ditonellapiaga</t>
+  </si>
+  <si>
+    <t>Sayf</t>
+  </si>
+  <si>
+    <t>Luchè</t>
+  </si>
+  <si>
+    <t>Tommaso Paradiso</t>
+  </si>
+  <si>
+    <t>Patty Pravo</t>
+  </si>
+  <si>
+    <t>Samurai Jay</t>
+  </si>
+  <si>
+    <t>Raf</t>
+  </si>
+  <si>
+    <t>J-Ax</t>
+  </si>
+  <si>
+    <t>Fedez e Masini</t>
+  </si>
+  <si>
+    <t>Nayt</t>
+  </si>
+  <si>
+    <t>Eddie Brock</t>
+  </si>
+  <si>
+    <t>Sal Da Vinci</t>
+  </si>
+  <si>
+    <t>Tredici Pietro</t>
+  </si>
+  <si>
+    <t>Chiello</t>
+  </si>
+  <si>
+    <t>Bambole di pezza</t>
+  </si>
+  <si>
+    <t>Maria Antonietta e Colombre</t>
+  </si>
+  <si>
+    <t>LDA e AKA 7even</t>
+  </si>
+  <si>
+    <t>LDA e AKA7even</t>
+  </si>
 </sst>
 </file>
 
@@ -935,7 +992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{668820A4-AEE7-984A-A205-7DC3CEADC66C}">
-  <dimension ref="A1:H821"/>
+  <dimension ref="A1:H941"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="38.5" bestFit="1" customWidth="1"/>
@@ -21498,7 +21555,3038 @@
         <v>12</v>
       </c>
     </row>
+    <row r="822" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A822">
+        <v>2026</v>
+      </c>
+      <c r="B822">
+        <v>1</v>
+      </c>
+      <c r="C822" t="s">
+        <v>8</v>
+      </c>
+      <c r="D822" t="s">
+        <v>176</v>
+      </c>
+      <c r="E822">
+        <v>1</v>
+      </c>
+      <c r="F822">
+        <v>30</v>
+      </c>
+      <c r="H822">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="823" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A823">
+        <v>2026</v>
+      </c>
+      <c r="B823">
+        <v>1</v>
+      </c>
+      <c r="C823" t="s">
+        <v>8</v>
+      </c>
+      <c r="D823" t="s">
+        <v>85</v>
+      </c>
+      <c r="E823">
+        <v>2</v>
+      </c>
+      <c r="F823">
+        <v>30</v>
+      </c>
+      <c r="H823">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="824" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A824">
+        <v>2026</v>
+      </c>
+      <c r="B824">
+        <v>1</v>
+      </c>
+      <c r="C824" t="s">
+        <v>8</v>
+      </c>
+      <c r="D824" t="s">
+        <v>177</v>
+      </c>
+      <c r="E824">
+        <v>3</v>
+      </c>
+      <c r="F824">
+        <v>30</v>
+      </c>
+      <c r="H824">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="825" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A825">
+        <v>2026</v>
+      </c>
+      <c r="B825">
+        <v>1</v>
+      </c>
+      <c r="C825" t="s">
+        <v>8</v>
+      </c>
+      <c r="D825" t="s">
+        <v>114</v>
+      </c>
+      <c r="E825">
+        <v>4</v>
+      </c>
+      <c r="F825">
+        <v>30</v>
+      </c>
+      <c r="H825">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="826" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A826">
+        <v>2026</v>
+      </c>
+      <c r="B826">
+        <v>1</v>
+      </c>
+      <c r="C826" t="s">
+        <v>8</v>
+      </c>
+      <c r="D826" t="s">
+        <v>90</v>
+      </c>
+      <c r="E826">
+        <v>5</v>
+      </c>
+      <c r="F826">
+        <v>30</v>
+      </c>
+      <c r="H826">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="827" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A827">
+        <v>2026</v>
+      </c>
+      <c r="B827">
+        <v>1</v>
+      </c>
+      <c r="C827" t="s">
+        <v>8</v>
+      </c>
+      <c r="D827" t="s">
+        <v>24</v>
+      </c>
+      <c r="E827">
+        <v>6</v>
+      </c>
+      <c r="F827">
+        <v>30</v>
+      </c>
+      <c r="H827">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="828" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A828">
+        <v>2026</v>
+      </c>
+      <c r="B828">
+        <v>1</v>
+      </c>
+      <c r="C828" t="s">
+        <v>8</v>
+      </c>
+      <c r="D828" t="s">
+        <v>178</v>
+      </c>
+      <c r="E828">
+        <v>7</v>
+      </c>
+      <c r="F828">
+        <v>30</v>
+      </c>
+      <c r="H828">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="829" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A829">
+        <v>2026</v>
+      </c>
+      <c r="B829">
+        <v>1</v>
+      </c>
+      <c r="C829" t="s">
+        <v>8</v>
+      </c>
+      <c r="D829" t="s">
+        <v>179</v>
+      </c>
+      <c r="E829">
+        <v>8</v>
+      </c>
+      <c r="F829">
+        <v>30</v>
+      </c>
+      <c r="H829">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="830" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A830">
+        <v>2026</v>
+      </c>
+      <c r="B830">
+        <v>1</v>
+      </c>
+      <c r="C830" t="s">
+        <v>8</v>
+      </c>
+      <c r="D830" t="s">
+        <v>49</v>
+      </c>
+      <c r="E830">
+        <v>9</v>
+      </c>
+      <c r="F830">
+        <v>30</v>
+      </c>
+      <c r="H830">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="831" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A831">
+        <v>2026</v>
+      </c>
+      <c r="B831">
+        <v>1</v>
+      </c>
+      <c r="C831" t="s">
+        <v>8</v>
+      </c>
+      <c r="D831" t="s">
+        <v>180</v>
+      </c>
+      <c r="E831">
+        <v>10</v>
+      </c>
+      <c r="F831">
+        <v>30</v>
+      </c>
+      <c r="H831">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="832" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A832">
+        <v>2026</v>
+      </c>
+      <c r="B832">
+        <v>1</v>
+      </c>
+      <c r="C832" t="s">
+        <v>8</v>
+      </c>
+      <c r="D832" t="s">
+        <v>181</v>
+      </c>
+      <c r="E832">
+        <v>11</v>
+      </c>
+      <c r="F832">
+        <v>30</v>
+      </c>
+      <c r="H832">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="833" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A833">
+        <v>2026</v>
+      </c>
+      <c r="B833">
+        <v>1</v>
+      </c>
+      <c r="C833" t="s">
+        <v>8</v>
+      </c>
+      <c r="D833" t="s">
+        <v>182</v>
+      </c>
+      <c r="E833">
+        <v>12</v>
+      </c>
+      <c r="F833">
+        <v>30</v>
+      </c>
+      <c r="H833">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="834" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A834">
+        <v>2026</v>
+      </c>
+      <c r="B834">
+        <v>1</v>
+      </c>
+      <c r="C834" t="s">
+        <v>8</v>
+      </c>
+      <c r="D834" t="s">
+        <v>183</v>
+      </c>
+      <c r="E834">
+        <v>13</v>
+      </c>
+      <c r="F834">
+        <v>30</v>
+      </c>
+      <c r="H834">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="835" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A835">
+        <v>2026</v>
+      </c>
+      <c r="B835">
+        <v>1</v>
+      </c>
+      <c r="C835" t="s">
+        <v>8</v>
+      </c>
+      <c r="D835" t="s">
+        <v>78</v>
+      </c>
+      <c r="E835">
+        <v>14</v>
+      </c>
+      <c r="F835">
+        <v>30</v>
+      </c>
+      <c r="H835">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="836" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A836">
+        <v>2026</v>
+      </c>
+      <c r="B836">
+        <v>1</v>
+      </c>
+      <c r="C836" t="s">
+        <v>8</v>
+      </c>
+      <c r="D836" t="s">
+        <v>50</v>
+      </c>
+      <c r="E836">
+        <v>15</v>
+      </c>
+      <c r="F836">
+        <v>30</v>
+      </c>
+      <c r="H836">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="837" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A837">
+        <v>2026</v>
+      </c>
+      <c r="B837">
+        <v>1</v>
+      </c>
+      <c r="C837" t="s">
+        <v>8</v>
+      </c>
+      <c r="D837" t="s">
+        <v>184</v>
+      </c>
+      <c r="E837">
+        <v>16</v>
+      </c>
+      <c r="F837">
+        <v>30</v>
+      </c>
+      <c r="H837">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="838" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A838">
+        <v>2026</v>
+      </c>
+      <c r="B838">
+        <v>1</v>
+      </c>
+      <c r="C838" t="s">
+        <v>8</v>
+      </c>
+      <c r="D838" t="s">
+        <v>75</v>
+      </c>
+      <c r="E838">
+        <v>17</v>
+      </c>
+      <c r="F838">
+        <v>30</v>
+      </c>
+      <c r="H838">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="839" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A839">
+        <v>2026</v>
+      </c>
+      <c r="B839">
+        <v>1</v>
+      </c>
+      <c r="C839" t="s">
+        <v>8</v>
+      </c>
+      <c r="D839" t="s">
+        <v>147</v>
+      </c>
+      <c r="E839">
+        <v>18</v>
+      </c>
+      <c r="F839">
+        <v>30</v>
+      </c>
+      <c r="H839">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="840" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A840">
+        <v>2026</v>
+      </c>
+      <c r="B840">
+        <v>1</v>
+      </c>
+      <c r="C840" t="s">
+        <v>8</v>
+      </c>
+      <c r="D840" t="s">
+        <v>185</v>
+      </c>
+      <c r="E840">
+        <v>19</v>
+      </c>
+      <c r="F840">
+        <v>30</v>
+      </c>
+      <c r="H840">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="841" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A841">
+        <v>2026</v>
+      </c>
+      <c r="B841">
+        <v>1</v>
+      </c>
+      <c r="C841" t="s">
+        <v>8</v>
+      </c>
+      <c r="D841" t="s">
+        <v>74</v>
+      </c>
+      <c r="E841">
+        <v>20</v>
+      </c>
+      <c r="F841">
+        <v>30</v>
+      </c>
+      <c r="H841">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="842" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A842">
+        <v>2026</v>
+      </c>
+      <c r="B842">
+        <v>1</v>
+      </c>
+      <c r="C842" t="s">
+        <v>8</v>
+      </c>
+      <c r="D842" t="s">
+        <v>186</v>
+      </c>
+      <c r="E842">
+        <v>21</v>
+      </c>
+      <c r="F842">
+        <v>30</v>
+      </c>
+      <c r="H842">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="843" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A843">
+        <v>2026</v>
+      </c>
+      <c r="B843">
+        <v>1</v>
+      </c>
+      <c r="C843" t="s">
+        <v>8</v>
+      </c>
+      <c r="D843" t="s">
+        <v>187</v>
+      </c>
+      <c r="E843">
+        <v>22</v>
+      </c>
+      <c r="F843">
+        <v>30</v>
+      </c>
+      <c r="H843">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="844" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A844">
+        <v>2026</v>
+      </c>
+      <c r="B844">
+        <v>1</v>
+      </c>
+      <c r="C844" t="s">
+        <v>8</v>
+      </c>
+      <c r="D844" t="s">
+        <v>31</v>
+      </c>
+      <c r="E844">
+        <v>23</v>
+      </c>
+      <c r="F844">
+        <v>30</v>
+      </c>
+      <c r="H844">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="845" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A845">
+        <v>2026</v>
+      </c>
+      <c r="B845">
+        <v>1</v>
+      </c>
+      <c r="C845" t="s">
+        <v>8</v>
+      </c>
+      <c r="D845" t="s">
+        <v>188</v>
+      </c>
+      <c r="E845">
+        <v>24</v>
+      </c>
+      <c r="F845">
+        <v>30</v>
+      </c>
+      <c r="H845">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="846" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A846">
+        <v>2026</v>
+      </c>
+      <c r="B846">
+        <v>1</v>
+      </c>
+      <c r="C846" t="s">
+        <v>8</v>
+      </c>
+      <c r="D846" t="s">
+        <v>189</v>
+      </c>
+      <c r="E846">
+        <v>25</v>
+      </c>
+      <c r="F846">
+        <v>30</v>
+      </c>
+      <c r="H846">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="847" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A847">
+        <v>2026</v>
+      </c>
+      <c r="B847">
+        <v>1</v>
+      </c>
+      <c r="C847" t="s">
+        <v>8</v>
+      </c>
+      <c r="D847" t="s">
+        <v>190</v>
+      </c>
+      <c r="E847">
+        <v>26</v>
+      </c>
+      <c r="F847">
+        <v>30</v>
+      </c>
+      <c r="H847">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="848" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A848">
+        <v>2026</v>
+      </c>
+      <c r="B848">
+        <v>1</v>
+      </c>
+      <c r="C848" t="s">
+        <v>8</v>
+      </c>
+      <c r="D848" t="s">
+        <v>191</v>
+      </c>
+      <c r="E848">
+        <v>27</v>
+      </c>
+      <c r="F848">
+        <v>30</v>
+      </c>
+      <c r="H848">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="849" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A849">
+        <v>2026</v>
+      </c>
+      <c r="B849">
+        <v>1</v>
+      </c>
+      <c r="C849" t="s">
+        <v>8</v>
+      </c>
+      <c r="D849" t="s">
+        <v>109</v>
+      </c>
+      <c r="E849">
+        <v>28</v>
+      </c>
+      <c r="F849">
+        <v>30</v>
+      </c>
+      <c r="H849">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="850" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A850">
+        <v>2026</v>
+      </c>
+      <c r="B850">
+        <v>1</v>
+      </c>
+      <c r="C850" t="s">
+        <v>8</v>
+      </c>
+      <c r="D850" t="s">
+        <v>9</v>
+      </c>
+      <c r="E850">
+        <v>29</v>
+      </c>
+      <c r="F850">
+        <v>30</v>
+      </c>
+      <c r="H850">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="851" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A851">
+        <v>2026</v>
+      </c>
+      <c r="B851">
+        <v>1</v>
+      </c>
+      <c r="C851" t="s">
+        <v>8</v>
+      </c>
+      <c r="D851" t="s">
+        <v>192</v>
+      </c>
+      <c r="E851">
+        <v>30</v>
+      </c>
+      <c r="F851">
+        <v>30</v>
+      </c>
+      <c r="H851">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="852" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A852">
+        <v>2026</v>
+      </c>
+      <c r="B852">
+        <v>2</v>
+      </c>
+      <c r="C852" t="s">
+        <v>33</v>
+      </c>
+      <c r="D852" t="s">
+        <v>180</v>
+      </c>
+      <c r="E852">
+        <v>1</v>
+      </c>
+      <c r="F852">
+        <v>15</v>
+      </c>
+      <c r="G852">
+        <v>13</v>
+      </c>
+      <c r="H852">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="853" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A853">
+        <v>2026</v>
+      </c>
+      <c r="B853">
+        <v>2</v>
+      </c>
+      <c r="C853" t="s">
+        <v>33</v>
+      </c>
+      <c r="D853" t="s">
+        <v>192</v>
+      </c>
+      <c r="E853">
+        <v>2</v>
+      </c>
+      <c r="F853">
+        <v>15</v>
+      </c>
+      <c r="G853">
+        <v>4</v>
+      </c>
+      <c r="H853">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="854" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A854">
+        <v>2026</v>
+      </c>
+      <c r="B854">
+        <v>2</v>
+      </c>
+      <c r="C854" t="s">
+        <v>33</v>
+      </c>
+      <c r="D854" t="s">
+        <v>31</v>
+      </c>
+      <c r="E854">
+        <v>3</v>
+      </c>
+      <c r="F854">
+        <v>15</v>
+      </c>
+      <c r="G854">
+        <v>9</v>
+      </c>
+      <c r="H854">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="855" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A855">
+        <v>2026</v>
+      </c>
+      <c r="B855">
+        <v>2</v>
+      </c>
+      <c r="C855" t="s">
+        <v>33</v>
+      </c>
+      <c r="D855" t="s">
+        <v>179</v>
+      </c>
+      <c r="E855">
+        <v>4</v>
+      </c>
+      <c r="F855">
+        <v>15</v>
+      </c>
+      <c r="G855">
+        <v>5</v>
+      </c>
+      <c r="H855">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="856" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A856">
+        <v>2026</v>
+      </c>
+      <c r="B856">
+        <v>2</v>
+      </c>
+      <c r="C856" t="s">
+        <v>33</v>
+      </c>
+      <c r="D856" t="s">
+        <v>49</v>
+      </c>
+      <c r="E856">
+        <v>5</v>
+      </c>
+      <c r="F856">
+        <v>15</v>
+      </c>
+      <c r="G856">
+        <v>14</v>
+      </c>
+      <c r="H856">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="857" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A857">
+        <v>2026</v>
+      </c>
+      <c r="B857">
+        <v>2</v>
+      </c>
+      <c r="C857" t="s">
+        <v>33</v>
+      </c>
+      <c r="D857" t="s">
+        <v>75</v>
+      </c>
+      <c r="E857">
+        <v>6</v>
+      </c>
+      <c r="F857">
+        <v>15</v>
+      </c>
+      <c r="G857">
+        <v>3</v>
+      </c>
+      <c r="H857">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="858" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A858">
+        <v>2026</v>
+      </c>
+      <c r="B858">
+        <v>2</v>
+      </c>
+      <c r="C858" t="s">
+        <v>33</v>
+      </c>
+      <c r="D858" t="s">
+        <v>50</v>
+      </c>
+      <c r="E858">
+        <v>7</v>
+      </c>
+      <c r="F858">
+        <v>15</v>
+      </c>
+      <c r="G858">
+        <v>10</v>
+      </c>
+      <c r="H858">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="859" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A859">
+        <v>2026</v>
+      </c>
+      <c r="B859">
+        <v>2</v>
+      </c>
+      <c r="C859" t="s">
+        <v>33</v>
+      </c>
+      <c r="D859" t="s">
+        <v>190</v>
+      </c>
+      <c r="E859">
+        <v>8</v>
+      </c>
+      <c r="F859">
+        <v>15</v>
+      </c>
+      <c r="G859">
+        <v>8</v>
+      </c>
+      <c r="H859">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="860" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A860">
+        <v>2026</v>
+      </c>
+      <c r="B860">
+        <v>2</v>
+      </c>
+      <c r="C860" t="s">
+        <v>33</v>
+      </c>
+      <c r="D860" t="s">
+        <v>189</v>
+      </c>
+      <c r="E860">
+        <v>9</v>
+      </c>
+      <c r="F860">
+        <v>15</v>
+      </c>
+      <c r="G860">
+        <v>12</v>
+      </c>
+      <c r="H860">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="861" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A861">
+        <v>2026</v>
+      </c>
+      <c r="B861">
+        <v>2</v>
+      </c>
+      <c r="C861" t="s">
+        <v>33</v>
+      </c>
+      <c r="D861" t="s">
+        <v>183</v>
+      </c>
+      <c r="E861">
+        <v>10</v>
+      </c>
+      <c r="F861">
+        <v>15</v>
+      </c>
+      <c r="G861">
+        <v>11</v>
+      </c>
+      <c r="H861">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="862" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A862">
+        <v>2026</v>
+      </c>
+      <c r="B862">
+        <v>2</v>
+      </c>
+      <c r="C862" t="s">
+        <v>33</v>
+      </c>
+      <c r="D862" t="s">
+        <v>185</v>
+      </c>
+      <c r="E862">
+        <v>11</v>
+      </c>
+      <c r="F862">
+        <v>15</v>
+      </c>
+      <c r="G862">
+        <v>1</v>
+      </c>
+      <c r="H862">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="863" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A863">
+        <v>2026</v>
+      </c>
+      <c r="B863">
+        <v>2</v>
+      </c>
+      <c r="C863" t="s">
+        <v>33</v>
+      </c>
+      <c r="D863" t="s">
+        <v>78</v>
+      </c>
+      <c r="E863">
+        <v>12</v>
+      </c>
+      <c r="F863">
+        <v>15</v>
+      </c>
+      <c r="G863">
+        <v>6</v>
+      </c>
+      <c r="H863">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="864" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A864">
+        <v>2026</v>
+      </c>
+      <c r="B864">
+        <v>2</v>
+      </c>
+      <c r="C864" t="s">
+        <v>33</v>
+      </c>
+      <c r="D864" t="s">
+        <v>184</v>
+      </c>
+      <c r="E864">
+        <v>13</v>
+      </c>
+      <c r="F864">
+        <v>15</v>
+      </c>
+      <c r="G864">
+        <v>2</v>
+      </c>
+      <c r="H864">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="865" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A865">
+        <v>2026</v>
+      </c>
+      <c r="B865">
+        <v>2</v>
+      </c>
+      <c r="C865" t="s">
+        <v>33</v>
+      </c>
+      <c r="D865" t="s">
+        <v>90</v>
+      </c>
+      <c r="E865">
+        <v>14</v>
+      </c>
+      <c r="F865">
+        <v>15</v>
+      </c>
+      <c r="G865">
+        <v>15</v>
+      </c>
+      <c r="H865">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="866" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A866">
+        <v>2026</v>
+      </c>
+      <c r="B866">
+        <v>2</v>
+      </c>
+      <c r="C866" t="s">
+        <v>33</v>
+      </c>
+      <c r="D866" t="s">
+        <v>176</v>
+      </c>
+      <c r="E866">
+        <v>15</v>
+      </c>
+      <c r="F866">
+        <v>15</v>
+      </c>
+      <c r="G866">
+        <v>7</v>
+      </c>
+      <c r="H866">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="867" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A867">
+        <v>2026</v>
+      </c>
+      <c r="B867">
+        <v>3</v>
+      </c>
+      <c r="C867" t="s">
+        <v>34</v>
+      </c>
+      <c r="D867" t="s">
+        <v>191</v>
+      </c>
+      <c r="E867">
+        <v>1</v>
+      </c>
+      <c r="F867">
+        <v>15</v>
+      </c>
+      <c r="G867">
+        <v>14</v>
+      </c>
+      <c r="H867">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="868" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A868">
+        <v>2026</v>
+      </c>
+      <c r="B868">
+        <v>3</v>
+      </c>
+      <c r="C868" t="s">
+        <v>34</v>
+      </c>
+      <c r="D868" t="s">
+        <v>109</v>
+      </c>
+      <c r="E868">
+        <v>2</v>
+      </c>
+      <c r="F868">
+        <v>15</v>
+      </c>
+      <c r="G868">
+        <v>11</v>
+      </c>
+      <c r="H868">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="869" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A869">
+        <v>2026</v>
+      </c>
+      <c r="B869">
+        <v>3</v>
+      </c>
+      <c r="C869" t="s">
+        <v>34</v>
+      </c>
+      <c r="D869" t="s">
+        <v>74</v>
+      </c>
+      <c r="E869">
+        <v>3</v>
+      </c>
+      <c r="F869">
+        <v>15</v>
+      </c>
+      <c r="G869">
+        <v>13</v>
+      </c>
+      <c r="H869">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="870" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A870">
+        <v>2026</v>
+      </c>
+      <c r="B870">
+        <v>3</v>
+      </c>
+      <c r="C870" t="s">
+        <v>34</v>
+      </c>
+      <c r="D870" t="s">
+        <v>187</v>
+      </c>
+      <c r="E870">
+        <v>4</v>
+      </c>
+      <c r="F870">
+        <v>15</v>
+      </c>
+      <c r="G870">
+        <v>1</v>
+      </c>
+      <c r="H870">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="871" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A871">
+        <v>2026</v>
+      </c>
+      <c r="B871">
+        <v>3</v>
+      </c>
+      <c r="C871" t="s">
+        <v>34</v>
+      </c>
+      <c r="D871" t="s">
+        <v>188</v>
+      </c>
+      <c r="E871">
+        <v>5</v>
+      </c>
+      <c r="F871">
+        <v>15</v>
+      </c>
+      <c r="G871">
+        <v>7</v>
+      </c>
+      <c r="H871">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="872" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A872">
+        <v>2026</v>
+      </c>
+      <c r="B872">
+        <v>3</v>
+      </c>
+      <c r="C872" t="s">
+        <v>34</v>
+      </c>
+      <c r="D872" t="s">
+        <v>182</v>
+      </c>
+      <c r="E872">
+        <v>6</v>
+      </c>
+      <c r="F872">
+        <v>15</v>
+      </c>
+      <c r="G872">
+        <v>8</v>
+      </c>
+      <c r="H872">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="873" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A873">
+        <v>2026</v>
+      </c>
+      <c r="B873">
+        <v>3</v>
+      </c>
+      <c r="C873" t="s">
+        <v>34</v>
+      </c>
+      <c r="D873" t="s">
+        <v>9</v>
+      </c>
+      <c r="E873">
+        <v>7</v>
+      </c>
+      <c r="F873">
+        <v>15</v>
+      </c>
+      <c r="G873">
+        <v>9</v>
+      </c>
+      <c r="H873">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="874" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A874">
+        <v>2026</v>
+      </c>
+      <c r="B874">
+        <v>3</v>
+      </c>
+      <c r="C874" t="s">
+        <v>34</v>
+      </c>
+      <c r="D874" t="s">
+        <v>186</v>
+      </c>
+      <c r="E874">
+        <v>8</v>
+      </c>
+      <c r="F874">
+        <v>15</v>
+      </c>
+      <c r="G874">
+        <v>12</v>
+      </c>
+      <c r="H874">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="875" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A875">
+        <v>2026</v>
+      </c>
+      <c r="B875">
+        <v>3</v>
+      </c>
+      <c r="C875" t="s">
+        <v>34</v>
+      </c>
+      <c r="D875" t="s">
+        <v>147</v>
+      </c>
+      <c r="E875">
+        <v>9</v>
+      </c>
+      <c r="F875">
+        <v>15</v>
+      </c>
+      <c r="G875">
+        <v>5</v>
+      </c>
+      <c r="H875">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="876" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A876">
+        <v>2026</v>
+      </c>
+      <c r="B876">
+        <v>3</v>
+      </c>
+      <c r="C876" t="s">
+        <v>34</v>
+      </c>
+      <c r="D876" t="s">
+        <v>181</v>
+      </c>
+      <c r="E876">
+        <v>10</v>
+      </c>
+      <c r="F876">
+        <v>15</v>
+      </c>
+      <c r="G876">
+        <v>6</v>
+      </c>
+      <c r="H876">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="877" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A877">
+        <v>2026</v>
+      </c>
+      <c r="B877">
+        <v>3</v>
+      </c>
+      <c r="C877" t="s">
+        <v>34</v>
+      </c>
+      <c r="D877" t="s">
+        <v>24</v>
+      </c>
+      <c r="E877">
+        <v>11</v>
+      </c>
+      <c r="F877">
+        <v>15</v>
+      </c>
+      <c r="G877">
+        <v>2</v>
+      </c>
+      <c r="H877">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="878" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A878">
+        <v>2026</v>
+      </c>
+      <c r="B878">
+        <v>3</v>
+      </c>
+      <c r="C878" t="s">
+        <v>34</v>
+      </c>
+      <c r="D878" t="s">
+        <v>85</v>
+      </c>
+      <c r="E878">
+        <v>12</v>
+      </c>
+      <c r="F878">
+        <v>15</v>
+      </c>
+      <c r="G878">
+        <v>10</v>
+      </c>
+      <c r="H878">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="879" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A879">
+        <v>2026</v>
+      </c>
+      <c r="B879">
+        <v>3</v>
+      </c>
+      <c r="C879" t="s">
+        <v>34</v>
+      </c>
+      <c r="D879" t="s">
+        <v>178</v>
+      </c>
+      <c r="E879">
+        <v>13</v>
+      </c>
+      <c r="F879">
+        <v>15</v>
+      </c>
+      <c r="G879">
+        <v>4</v>
+      </c>
+      <c r="H879">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="880" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A880">
+        <v>2026</v>
+      </c>
+      <c r="B880">
+        <v>3</v>
+      </c>
+      <c r="C880" t="s">
+        <v>34</v>
+      </c>
+      <c r="D880" t="s">
+        <v>114</v>
+      </c>
+      <c r="E880">
+        <v>14</v>
+      </c>
+      <c r="F880">
+        <v>15</v>
+      </c>
+      <c r="G880">
+        <v>15</v>
+      </c>
+      <c r="H880">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="881" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A881">
+        <v>2026</v>
+      </c>
+      <c r="B881">
+        <v>3</v>
+      </c>
+      <c r="C881" t="s">
+        <v>34</v>
+      </c>
+      <c r="D881" t="s">
+        <v>177</v>
+      </c>
+      <c r="E881">
+        <v>15</v>
+      </c>
+      <c r="F881">
+        <v>15</v>
+      </c>
+      <c r="G881">
+        <v>3</v>
+      </c>
+      <c r="H881">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="882" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A882">
+        <v>2026</v>
+      </c>
+      <c r="B882">
+        <v>4</v>
+      </c>
+      <c r="C882" t="s">
+        <v>35</v>
+      </c>
+      <c r="D882" t="s">
+        <v>49</v>
+      </c>
+      <c r="E882">
+        <v>1</v>
+      </c>
+      <c r="F882">
+        <v>30</v>
+      </c>
+      <c r="G882">
+        <v>14</v>
+      </c>
+      <c r="H882">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="883" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A883">
+        <v>2026</v>
+      </c>
+      <c r="B883">
+        <v>4</v>
+      </c>
+      <c r="C883" t="s">
+        <v>35</v>
+      </c>
+      <c r="D883" t="s">
+        <v>186</v>
+      </c>
+      <c r="E883">
+        <v>2</v>
+      </c>
+      <c r="F883">
+        <v>30</v>
+      </c>
+      <c r="G883">
+        <v>21</v>
+      </c>
+      <c r="H883">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="884" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A884">
+        <v>2026</v>
+      </c>
+      <c r="B884">
+        <v>4</v>
+      </c>
+      <c r="C884" t="s">
+        <v>35</v>
+      </c>
+      <c r="D884" t="s">
+        <v>114</v>
+      </c>
+      <c r="E884">
+        <v>3</v>
+      </c>
+      <c r="F884">
+        <v>30</v>
+      </c>
+      <c r="G884">
+        <v>29</v>
+      </c>
+      <c r="H884">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="885" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A885">
+        <v>2026</v>
+      </c>
+      <c r="B885">
+        <v>4</v>
+      </c>
+      <c r="C885" t="s">
+        <v>35</v>
+      </c>
+      <c r="D885" t="s">
+        <v>180</v>
+      </c>
+      <c r="E885">
+        <v>4</v>
+      </c>
+      <c r="F885">
+        <v>30</v>
+      </c>
+      <c r="G885">
+        <v>28</v>
+      </c>
+      <c r="H885">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="886" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A886">
+        <v>2026</v>
+      </c>
+      <c r="B886">
+        <v>4</v>
+      </c>
+      <c r="C886" t="s">
+        <v>35</v>
+      </c>
+      <c r="D886" t="s">
+        <v>50</v>
+      </c>
+      <c r="E886">
+        <v>5</v>
+      </c>
+      <c r="F886">
+        <v>30</v>
+      </c>
+      <c r="G886">
+        <v>19</v>
+      </c>
+      <c r="H886">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="887" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A887">
+        <v>2026</v>
+      </c>
+      <c r="B887">
+        <v>4</v>
+      </c>
+      <c r="C887" t="s">
+        <v>35</v>
+      </c>
+      <c r="D887" t="s">
+        <v>74</v>
+      </c>
+      <c r="E887">
+        <v>6</v>
+      </c>
+      <c r="F887">
+        <v>30</v>
+      </c>
+      <c r="G887">
+        <v>22</v>
+      </c>
+      <c r="H887">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="888" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A888">
+        <v>2026</v>
+      </c>
+      <c r="B888">
+        <v>4</v>
+      </c>
+      <c r="C888" t="s">
+        <v>35</v>
+      </c>
+      <c r="D888" t="s">
+        <v>190</v>
+      </c>
+      <c r="E888">
+        <v>7</v>
+      </c>
+      <c r="F888">
+        <v>30</v>
+      </c>
+      <c r="G888">
+        <v>5</v>
+      </c>
+      <c r="H888">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="889" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A889">
+        <v>2026</v>
+      </c>
+      <c r="B889">
+        <v>4</v>
+      </c>
+      <c r="C889" t="s">
+        <v>35</v>
+      </c>
+      <c r="D889" t="s">
+        <v>90</v>
+      </c>
+      <c r="E889">
+        <v>8</v>
+      </c>
+      <c r="F889">
+        <v>30</v>
+      </c>
+      <c r="G889">
+        <v>10</v>
+      </c>
+      <c r="H889">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="890" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A890">
+        <v>2026</v>
+      </c>
+      <c r="B890">
+        <v>4</v>
+      </c>
+      <c r="C890" t="s">
+        <v>35</v>
+      </c>
+      <c r="D890" t="s">
+        <v>179</v>
+      </c>
+      <c r="E890">
+        <v>9</v>
+      </c>
+      <c r="F890">
+        <v>30</v>
+      </c>
+      <c r="G890">
+        <v>15</v>
+      </c>
+      <c r="H890">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="891" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A891">
+        <v>2026</v>
+      </c>
+      <c r="B891">
+        <v>4</v>
+      </c>
+      <c r="C891" t="s">
+        <v>35</v>
+      </c>
+      <c r="D891" t="s">
+        <v>85</v>
+      </c>
+      <c r="E891">
+        <v>10</v>
+      </c>
+      <c r="F891">
+        <v>30</v>
+      </c>
+      <c r="G891">
+        <v>16</v>
+      </c>
+      <c r="H891">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="892" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A892">
+        <v>2026</v>
+      </c>
+      <c r="B892">
+        <v>4</v>
+      </c>
+      <c r="C892" t="s">
+        <v>35</v>
+      </c>
+      <c r="D892" t="s">
+        <v>188</v>
+      </c>
+      <c r="E892">
+        <v>11</v>
+      </c>
+      <c r="F892">
+        <v>30</v>
+      </c>
+      <c r="G892">
+        <v>6</v>
+      </c>
+      <c r="H892">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="893" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A893">
+        <v>2026</v>
+      </c>
+      <c r="B893">
+        <v>4</v>
+      </c>
+      <c r="C893" t="s">
+        <v>35</v>
+      </c>
+      <c r="D893" t="s">
+        <v>191</v>
+      </c>
+      <c r="E893">
+        <v>12</v>
+      </c>
+      <c r="F893">
+        <v>30</v>
+      </c>
+      <c r="G893">
+        <v>24</v>
+      </c>
+      <c r="H893">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="894" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A894">
+        <v>2026</v>
+      </c>
+      <c r="B894">
+        <v>4</v>
+      </c>
+      <c r="C894" t="s">
+        <v>35</v>
+      </c>
+      <c r="D894" t="s">
+        <v>78</v>
+      </c>
+      <c r="E894">
+        <v>13</v>
+      </c>
+      <c r="F894">
+        <v>30</v>
+      </c>
+      <c r="G894">
+        <v>13</v>
+      </c>
+      <c r="H894">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="895" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A895">
+        <v>2026</v>
+      </c>
+      <c r="B895">
+        <v>4</v>
+      </c>
+      <c r="C895" t="s">
+        <v>35</v>
+      </c>
+      <c r="D895" t="s">
+        <v>192</v>
+      </c>
+      <c r="E895">
+        <v>14</v>
+      </c>
+      <c r="F895">
+        <v>30</v>
+      </c>
+      <c r="G895">
+        <v>8</v>
+      </c>
+      <c r="H895">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="896" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A896">
+        <v>2026</v>
+      </c>
+      <c r="B896">
+        <v>4</v>
+      </c>
+      <c r="C896" t="s">
+        <v>35</v>
+      </c>
+      <c r="D896" t="s">
+        <v>182</v>
+      </c>
+      <c r="E896">
+        <v>15</v>
+      </c>
+      <c r="F896">
+        <v>30</v>
+      </c>
+      <c r="G896">
+        <v>26</v>
+      </c>
+      <c r="H896">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="897" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A897">
+        <v>2026</v>
+      </c>
+      <c r="B897">
+        <v>4</v>
+      </c>
+      <c r="C897" t="s">
+        <v>35</v>
+      </c>
+      <c r="D897" t="s">
+        <v>183</v>
+      </c>
+      <c r="E897">
+        <v>16</v>
+      </c>
+      <c r="F897">
+        <v>30</v>
+      </c>
+      <c r="G897">
+        <v>18</v>
+      </c>
+      <c r="H897">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="898" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A898">
+        <v>2026</v>
+      </c>
+      <c r="B898">
+        <v>4</v>
+      </c>
+      <c r="C898" t="s">
+        <v>35</v>
+      </c>
+      <c r="D898" t="s">
+        <v>176</v>
+      </c>
+      <c r="E898">
+        <v>17</v>
+      </c>
+      <c r="F898">
+        <v>30</v>
+      </c>
+      <c r="G898">
+        <v>1</v>
+      </c>
+      <c r="H898">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="899" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A899">
+        <v>2026</v>
+      </c>
+      <c r="B899">
+        <v>4</v>
+      </c>
+      <c r="C899" t="s">
+        <v>35</v>
+      </c>
+      <c r="D899" t="s">
+        <v>31</v>
+      </c>
+      <c r="E899">
+        <v>18</v>
+      </c>
+      <c r="F899">
+        <v>30</v>
+      </c>
+      <c r="G899">
+        <v>11</v>
+      </c>
+      <c r="H899">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="900" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A900">
+        <v>2026</v>
+      </c>
+      <c r="B900">
+        <v>4</v>
+      </c>
+      <c r="C900" t="s">
+        <v>35</v>
+      </c>
+      <c r="D900" t="s">
+        <v>147</v>
+      </c>
+      <c r="E900">
+        <v>19</v>
+      </c>
+      <c r="F900">
+        <v>30</v>
+      </c>
+      <c r="G900">
+        <v>17</v>
+      </c>
+      <c r="H900">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="901" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A901">
+        <v>2026</v>
+      </c>
+      <c r="B901">
+        <v>4</v>
+      </c>
+      <c r="C901" t="s">
+        <v>35</v>
+      </c>
+      <c r="D901" t="s">
+        <v>177</v>
+      </c>
+      <c r="E901">
+        <v>20</v>
+      </c>
+      <c r="F901">
+        <v>30</v>
+      </c>
+      <c r="G901">
+        <v>2</v>
+      </c>
+      <c r="H901">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="902" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A902">
+        <v>2026</v>
+      </c>
+      <c r="B902">
+        <v>4</v>
+      </c>
+      <c r="C902" t="s">
+        <v>35</v>
+      </c>
+      <c r="D902" t="s">
+        <v>9</v>
+      </c>
+      <c r="E902">
+        <v>21</v>
+      </c>
+      <c r="F902">
+        <v>30</v>
+      </c>
+      <c r="G902">
+        <v>30</v>
+      </c>
+      <c r="H902">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="903" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A903">
+        <v>2026</v>
+      </c>
+      <c r="B903">
+        <v>4</v>
+      </c>
+      <c r="C903" t="s">
+        <v>35</v>
+      </c>
+      <c r="D903" t="s">
+        <v>24</v>
+      </c>
+      <c r="E903">
+        <v>22</v>
+      </c>
+      <c r="F903">
+        <v>30</v>
+      </c>
+      <c r="G903">
+        <v>3</v>
+      </c>
+      <c r="H903">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="904" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A904">
+        <v>2026</v>
+      </c>
+      <c r="B904">
+        <v>4</v>
+      </c>
+      <c r="C904" t="s">
+        <v>35</v>
+      </c>
+      <c r="D904" t="s">
+        <v>181</v>
+      </c>
+      <c r="E904">
+        <v>23</v>
+      </c>
+      <c r="F904">
+        <v>30</v>
+      </c>
+      <c r="G904">
+        <v>23</v>
+      </c>
+      <c r="H904">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="905" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A905">
+        <v>2026</v>
+      </c>
+      <c r="B905">
+        <v>4</v>
+      </c>
+      <c r="C905" t="s">
+        <v>35</v>
+      </c>
+      <c r="D905" t="s">
+        <v>187</v>
+      </c>
+      <c r="E905">
+        <v>24</v>
+      </c>
+      <c r="F905">
+        <v>30</v>
+      </c>
+      <c r="G905">
+        <v>4</v>
+      </c>
+      <c r="H905">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="906" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A906">
+        <v>2026</v>
+      </c>
+      <c r="B906">
+        <v>4</v>
+      </c>
+      <c r="C906" t="s">
+        <v>35</v>
+      </c>
+      <c r="D906" t="s">
+        <v>184</v>
+      </c>
+      <c r="E906">
+        <v>25</v>
+      </c>
+      <c r="F906">
+        <v>30</v>
+      </c>
+      <c r="G906">
+        <v>12</v>
+      </c>
+      <c r="H906">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="907" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A907">
+        <v>2026</v>
+      </c>
+      <c r="B907">
+        <v>4</v>
+      </c>
+      <c r="C907" t="s">
+        <v>35</v>
+      </c>
+      <c r="D907" t="s">
+        <v>75</v>
+      </c>
+      <c r="E907">
+        <v>26</v>
+      </c>
+      <c r="F907">
+        <v>30</v>
+      </c>
+      <c r="G907">
+        <v>20</v>
+      </c>
+      <c r="H907">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="908" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A908">
+        <v>2026</v>
+      </c>
+      <c r="B908">
+        <v>4</v>
+      </c>
+      <c r="C908" t="s">
+        <v>35</v>
+      </c>
+      <c r="D908" t="s">
+        <v>185</v>
+      </c>
+      <c r="E908">
+        <v>27</v>
+      </c>
+      <c r="F908">
+        <v>30</v>
+      </c>
+      <c r="G908">
+        <v>7</v>
+      </c>
+      <c r="H908">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="909" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A909">
+        <v>2026</v>
+      </c>
+      <c r="B909">
+        <v>4</v>
+      </c>
+      <c r="C909" t="s">
+        <v>35</v>
+      </c>
+      <c r="D909" t="s">
+        <v>178</v>
+      </c>
+      <c r="E909">
+        <v>28</v>
+      </c>
+      <c r="F909">
+        <v>30</v>
+      </c>
+      <c r="G909">
+        <v>9</v>
+      </c>
+      <c r="H909">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="910" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A910">
+        <v>2026</v>
+      </c>
+      <c r="B910">
+        <v>4</v>
+      </c>
+      <c r="C910" t="s">
+        <v>35</v>
+      </c>
+      <c r="D910" t="s">
+        <v>189</v>
+      </c>
+      <c r="E910">
+        <v>29</v>
+      </c>
+      <c r="F910">
+        <v>30</v>
+      </c>
+      <c r="G910">
+        <v>27</v>
+      </c>
+      <c r="H910">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="911" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A911">
+        <v>2026</v>
+      </c>
+      <c r="B911">
+        <v>4</v>
+      </c>
+      <c r="C911" t="s">
+        <v>35</v>
+      </c>
+      <c r="D911" t="s">
+        <v>109</v>
+      </c>
+      <c r="E911">
+        <v>30</v>
+      </c>
+      <c r="F911">
+        <v>30</v>
+      </c>
+      <c r="G911">
+        <v>25</v>
+      </c>
+      <c r="H911">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="912" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A912">
+        <v>2026</v>
+      </c>
+      <c r="B912">
+        <v>5</v>
+      </c>
+      <c r="C912" t="s">
+        <v>36</v>
+      </c>
+      <c r="D912" t="s">
+        <v>9</v>
+      </c>
+      <c r="E912">
+        <v>1</v>
+      </c>
+      <c r="F912">
+        <v>30</v>
+      </c>
+      <c r="G912">
+        <v>21</v>
+      </c>
+      <c r="H912">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="913" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A913">
+        <v>2026</v>
+      </c>
+      <c r="B913">
+        <v>5</v>
+      </c>
+      <c r="C913" t="s">
+        <v>36</v>
+      </c>
+      <c r="D913" t="s">
+        <v>189</v>
+      </c>
+      <c r="E913">
+        <v>2</v>
+      </c>
+      <c r="F913">
+        <v>30</v>
+      </c>
+      <c r="G913">
+        <v>20</v>
+      </c>
+      <c r="H913">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="914" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A914">
+        <v>2026</v>
+      </c>
+      <c r="B914">
+        <v>5</v>
+      </c>
+      <c r="C914" t="s">
+        <v>36</v>
+      </c>
+      <c r="D914" t="s">
+        <v>182</v>
+      </c>
+      <c r="E914">
+        <v>3</v>
+      </c>
+      <c r="F914">
+        <v>30</v>
+      </c>
+      <c r="G914">
+        <v>17</v>
+      </c>
+      <c r="H914">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="915" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A915">
+        <v>2026</v>
+      </c>
+      <c r="B915">
+        <v>5</v>
+      </c>
+      <c r="C915" t="s">
+        <v>36</v>
+      </c>
+      <c r="D915" t="s">
+        <v>190</v>
+      </c>
+      <c r="E915">
+        <v>4</v>
+      </c>
+      <c r="F915">
+        <v>30</v>
+      </c>
+      <c r="G915">
+        <v>13</v>
+      </c>
+      <c r="H915">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="916" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A916">
+        <v>2026</v>
+      </c>
+      <c r="B916">
+        <v>5</v>
+      </c>
+      <c r="C916" t="s">
+        <v>36</v>
+      </c>
+      <c r="D916" t="s">
+        <v>109</v>
+      </c>
+      <c r="E916">
+        <v>5</v>
+      </c>
+      <c r="F916">
+        <v>30</v>
+      </c>
+      <c r="G916">
+        <v>23</v>
+      </c>
+      <c r="H916">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="917" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A917">
+        <v>2026</v>
+      </c>
+      <c r="B917">
+        <v>5</v>
+      </c>
+      <c r="C917" t="s">
+        <v>36</v>
+      </c>
+      <c r="D917" t="s">
+        <v>74</v>
+      </c>
+      <c r="E917">
+        <v>6</v>
+      </c>
+      <c r="F917">
+        <v>30</v>
+      </c>
+      <c r="G917">
+        <v>24</v>
+      </c>
+      <c r="H917">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="918" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A918">
+        <v>2026</v>
+      </c>
+      <c r="B918">
+        <v>5</v>
+      </c>
+      <c r="C918" t="s">
+        <v>36</v>
+      </c>
+      <c r="D918" t="s">
+        <v>179</v>
+      </c>
+      <c r="E918">
+        <v>7</v>
+      </c>
+      <c r="F918">
+        <v>30</v>
+      </c>
+      <c r="G918">
+        <v>10</v>
+      </c>
+      <c r="H918">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="919" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A919">
+        <v>2026</v>
+      </c>
+      <c r="B919">
+        <v>5</v>
+      </c>
+      <c r="C919" t="s">
+        <v>36</v>
+      </c>
+      <c r="D919" t="s">
+        <v>183</v>
+      </c>
+      <c r="E919">
+        <v>8</v>
+      </c>
+      <c r="F919">
+        <v>30</v>
+      </c>
+      <c r="G919">
+        <v>15</v>
+      </c>
+      <c r="H919">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="920" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A920">
+        <v>2026</v>
+      </c>
+      <c r="B920">
+        <v>5</v>
+      </c>
+      <c r="C920" t="s">
+        <v>36</v>
+      </c>
+      <c r="D920" t="s">
+        <v>193</v>
+      </c>
+      <c r="E920">
+        <v>9</v>
+      </c>
+      <c r="F920">
+        <v>30</v>
+      </c>
+      <c r="G920">
+        <v>8</v>
+      </c>
+      <c r="H920">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="921" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A921">
+        <v>2026</v>
+      </c>
+      <c r="B921">
+        <v>5</v>
+      </c>
+      <c r="C921" t="s">
+        <v>36</v>
+      </c>
+      <c r="D921" t="s">
+        <v>147</v>
+      </c>
+      <c r="E921">
+        <v>10</v>
+      </c>
+      <c r="F921">
+        <v>30</v>
+      </c>
+      <c r="G921">
+        <v>11</v>
+      </c>
+      <c r="H921">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="922" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A922">
+        <v>2026</v>
+      </c>
+      <c r="B922">
+        <v>5</v>
+      </c>
+      <c r="C922" t="s">
+        <v>36</v>
+      </c>
+      <c r="D922" t="s">
+        <v>180</v>
+      </c>
+      <c r="E922">
+        <v>11</v>
+      </c>
+      <c r="F922">
+        <v>30</v>
+      </c>
+      <c r="G922">
+        <v>26</v>
+      </c>
+      <c r="H922">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="923" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A923">
+        <v>2026</v>
+      </c>
+      <c r="B923">
+        <v>5</v>
+      </c>
+      <c r="C923" t="s">
+        <v>36</v>
+      </c>
+      <c r="D923" t="s">
+        <v>187</v>
+      </c>
+      <c r="E923">
+        <v>12</v>
+      </c>
+      <c r="F923">
+        <v>30</v>
+      </c>
+      <c r="G923">
+        <v>1</v>
+      </c>
+      <c r="H923">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="924" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A924">
+        <v>2026</v>
+      </c>
+      <c r="B924">
+        <v>5</v>
+      </c>
+      <c r="C924" t="s">
+        <v>36</v>
+      </c>
+      <c r="D924" t="s">
+        <v>49</v>
+      </c>
+      <c r="E924">
+        <v>13</v>
+      </c>
+      <c r="F924">
+        <v>30</v>
+      </c>
+      <c r="G924">
+        <v>16</v>
+      </c>
+      <c r="H924">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="925" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A925">
+        <v>2026</v>
+      </c>
+      <c r="B925">
+        <v>5</v>
+      </c>
+      <c r="C925" t="s">
+        <v>36</v>
+      </c>
+      <c r="D925" t="s">
+        <v>75</v>
+      </c>
+      <c r="E925">
+        <v>14</v>
+      </c>
+      <c r="F925">
+        <v>30</v>
+      </c>
+      <c r="G925">
+        <v>7</v>
+      </c>
+      <c r="H925">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="926" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A926">
+        <v>2026</v>
+      </c>
+      <c r="B926">
+        <v>5</v>
+      </c>
+      <c r="C926" t="s">
+        <v>36</v>
+      </c>
+      <c r="D926" t="s">
+        <v>176</v>
+      </c>
+      <c r="E926">
+        <v>15</v>
+      </c>
+      <c r="F926">
+        <v>30</v>
+      </c>
+      <c r="G926">
+        <v>4</v>
+      </c>
+      <c r="H926">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="927" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A927">
+        <v>2026</v>
+      </c>
+      <c r="B927">
+        <v>5</v>
+      </c>
+      <c r="C927" t="s">
+        <v>36</v>
+      </c>
+      <c r="D927" t="s">
+        <v>185</v>
+      </c>
+      <c r="E927">
+        <v>16</v>
+      </c>
+      <c r="F927">
+        <v>30</v>
+      </c>
+      <c r="G927">
+        <v>6</v>
+      </c>
+      <c r="H927">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="928" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A928">
+        <v>2026</v>
+      </c>
+      <c r="B928">
+        <v>5</v>
+      </c>
+      <c r="C928" t="s">
+        <v>36</v>
+      </c>
+      <c r="D928" t="s">
+        <v>24</v>
+      </c>
+      <c r="E928">
+        <v>17</v>
+      </c>
+      <c r="F928">
+        <v>30</v>
+      </c>
+      <c r="G928">
+        <v>2</v>
+      </c>
+      <c r="H928">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="929" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A929">
+        <v>2026</v>
+      </c>
+      <c r="B929">
+        <v>5</v>
+      </c>
+      <c r="C929" t="s">
+        <v>36</v>
+      </c>
+      <c r="D929" t="s">
+        <v>177</v>
+      </c>
+      <c r="E929">
+        <v>18</v>
+      </c>
+      <c r="F929">
+        <v>30</v>
+      </c>
+      <c r="G929">
+        <v>3</v>
+      </c>
+      <c r="H929">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="930" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A930">
+        <v>2026</v>
+      </c>
+      <c r="B930">
+        <v>5</v>
+      </c>
+      <c r="C930" t="s">
+        <v>36</v>
+      </c>
+      <c r="D930" t="s">
+        <v>50</v>
+      </c>
+      <c r="E930">
+        <v>19</v>
+      </c>
+      <c r="F930">
+        <v>30</v>
+      </c>
+      <c r="G930">
+        <v>19</v>
+      </c>
+      <c r="H930">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="931" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A931">
+        <v>2026</v>
+      </c>
+      <c r="B931">
+        <v>5</v>
+      </c>
+      <c r="C931" t="s">
+        <v>36</v>
+      </c>
+      <c r="D931" t="s">
+        <v>184</v>
+      </c>
+      <c r="E931">
+        <v>20</v>
+      </c>
+      <c r="F931">
+        <v>30</v>
+      </c>
+      <c r="G931">
+        <v>5</v>
+      </c>
+      <c r="H931">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="932" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A932">
+        <v>2026</v>
+      </c>
+      <c r="B932">
+        <v>5</v>
+      </c>
+      <c r="C932" t="s">
+        <v>36</v>
+      </c>
+      <c r="D932" t="s">
+        <v>181</v>
+      </c>
+      <c r="E932">
+        <v>21</v>
+      </c>
+      <c r="F932">
+        <v>30</v>
+      </c>
+      <c r="G932">
+        <v>14</v>
+      </c>
+      <c r="H932">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="933" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A933">
+        <v>2026</v>
+      </c>
+      <c r="B933">
+        <v>5</v>
+      </c>
+      <c r="C933" t="s">
+        <v>36</v>
+      </c>
+      <c r="D933" t="s">
+        <v>85</v>
+      </c>
+      <c r="E933">
+        <v>22</v>
+      </c>
+      <c r="F933">
+        <v>30</v>
+      </c>
+      <c r="G933">
+        <v>22</v>
+      </c>
+      <c r="H933">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="934" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A934">
+        <v>2026</v>
+      </c>
+      <c r="B934">
+        <v>5</v>
+      </c>
+      <c r="C934" t="s">
+        <v>36</v>
+      </c>
+      <c r="D934" t="s">
+        <v>78</v>
+      </c>
+      <c r="E934">
+        <v>23</v>
+      </c>
+      <c r="F934">
+        <v>30</v>
+      </c>
+      <c r="G934">
+        <v>9</v>
+      </c>
+      <c r="H934">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="935" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A935">
+        <v>2026</v>
+      </c>
+      <c r="B935">
+        <v>5</v>
+      </c>
+      <c r="C935" t="s">
+        <v>36</v>
+      </c>
+      <c r="D935" t="s">
+        <v>178</v>
+      </c>
+      <c r="E935">
+        <v>24</v>
+      </c>
+      <c r="F935">
+        <v>30</v>
+      </c>
+      <c r="G935">
+        <v>12</v>
+      </c>
+      <c r="H935">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="936" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A936">
+        <v>2026</v>
+      </c>
+      <c r="B936">
+        <v>5</v>
+      </c>
+      <c r="C936" t="s">
+        <v>36</v>
+      </c>
+      <c r="D936" t="s">
+        <v>188</v>
+      </c>
+      <c r="E936">
+        <v>25</v>
+      </c>
+      <c r="F936">
+        <v>30</v>
+      </c>
+      <c r="G936">
+        <v>18</v>
+      </c>
+      <c r="H936">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="937" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A937">
+        <v>2026</v>
+      </c>
+      <c r="B937">
+        <v>5</v>
+      </c>
+      <c r="C937" t="s">
+        <v>36</v>
+      </c>
+      <c r="D937" t="s">
+        <v>114</v>
+      </c>
+      <c r="E937">
+        <v>26</v>
+      </c>
+      <c r="F937">
+        <v>30</v>
+      </c>
+      <c r="G937">
+        <v>29</v>
+      </c>
+      <c r="H937">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="938" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A938">
+        <v>2026</v>
+      </c>
+      <c r="B938">
+        <v>5</v>
+      </c>
+      <c r="C938" t="s">
+        <v>36</v>
+      </c>
+      <c r="D938" t="s">
+        <v>90</v>
+      </c>
+      <c r="E938">
+        <v>27</v>
+      </c>
+      <c r="F938">
+        <v>30</v>
+      </c>
+      <c r="G938">
+        <v>28</v>
+      </c>
+      <c r="H938">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="939" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A939">
+        <v>2026</v>
+      </c>
+      <c r="B939">
+        <v>5</v>
+      </c>
+      <c r="C939" t="s">
+        <v>36</v>
+      </c>
+      <c r="D939" t="s">
+        <v>31</v>
+      </c>
+      <c r="E939">
+        <v>28</v>
+      </c>
+      <c r="F939">
+        <v>30</v>
+      </c>
+      <c r="G939">
+        <v>25</v>
+      </c>
+      <c r="H939">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="940" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A940">
+        <v>2026</v>
+      </c>
+      <c r="B940">
+        <v>5</v>
+      </c>
+      <c r="C940" t="s">
+        <v>36</v>
+      </c>
+      <c r="D940" t="s">
+        <v>191</v>
+      </c>
+      <c r="E940">
+        <v>29</v>
+      </c>
+      <c r="F940">
+        <v>30</v>
+      </c>
+      <c r="G940">
+        <v>30</v>
+      </c>
+      <c r="H940">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="941" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A941">
+        <v>2026</v>
+      </c>
+      <c r="B941">
+        <v>5</v>
+      </c>
+      <c r="C941" t="s">
+        <v>36</v>
+      </c>
+      <c r="D941" t="s">
+        <v>186</v>
+      </c>
+      <c r="E941">
+        <v>30</v>
+      </c>
+      <c r="F941">
+        <v>30</v>
+      </c>
+      <c r="G941">
+        <v>27</v>
+      </c>
+      <c r="H941">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:H941" xr:uid="{668820A4-AEE7-984A-A205-7DC3CEADC66C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>